--- a/investors.xlsx
+++ b/investors.xlsx
@@ -16,9 +16,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -49,9 +51,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1370,63 +1373,73 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>nikhil</t>
+          <t>Harshala Patole</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1212121212</v>
+        <v>987457352</v>
       </c>
       <c r="C2" s="1" t="n">
+        <v>46113</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>jmd 6.0</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2" t="n">
+        <v>500000</v>
+      </c>
+      <c r="H2" s="1" t="n">
+        <v>46387</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" s="1" t="n">
         <v>46143</v>
       </c>
-      <c r="D2" t="n">
-        <v>2000000</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>jmd 6.0</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G2" t="n">
-        <v>10000000</v>
-      </c>
-      <c r="H2" s="1" t="n">
-        <v>46166</v>
-      </c>
-      <c r="I2" t="b">
-        <v>1</v>
-      </c>
-      <c r="J2" s="1" t="n">
-        <v>46163</v>
-      </c>
       <c r="K2" t="b">
         <v>0</v>
       </c>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+      <c r="M2" s="1" t="n">
+        <v>46174</v>
+      </c>
       <c r="N2" t="b">
         <v>0</v>
       </c>
       <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
+      <c r="P2" s="1" t="n">
+        <v>46204</v>
+      </c>
       <c r="Q2" t="b">
         <v>0</v>
       </c>
       <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
+      <c r="S2" s="1" t="n">
+        <v>46235</v>
+      </c>
       <c r="T2" t="b">
         <v>0</v>
       </c>
       <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
+      <c r="V2" s="1" t="n">
+        <v>46266</v>
+      </c>
       <c r="W2" t="b">
         <v>0</v>
       </c>
       <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr"/>
+      <c r="Y2" s="1" t="n">
+        <v>46296</v>
+      </c>
       <c r="Z2" t="b">
         <v>0</v>
       </c>
@@ -1705,332 +1718,264 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Satish Patole</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" s="1" t="n">
+          <t>Ajay Bhosale</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>9874623097</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="D3" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>jmd 6.0</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>12</v>
+      </c>
+      <c r="G3" t="n">
+        <v>2500000</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>46508</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" s="2" t="n">
+        <v>46113</v>
+      </c>
+      <c r="K3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" s="2" t="n">
         <v>46143</v>
       </c>
-      <c r="D3" t="n">
-        <v>200000</v>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="n">
-        <v>2</v>
-      </c>
-      <c r="G3" t="n">
-        <v>100000</v>
-      </c>
-      <c r="H3" s="1" t="n">
-        <v>46265</v>
-      </c>
-      <c r="I3" t="b">
-        <v>1</v>
-      </c>
-      <c r="J3" s="1" t="n">
-        <v>46165</v>
-      </c>
-      <c r="K3" t="b">
-        <v>0</v>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" s="1" t="n">
-        <v>46192</v>
-      </c>
       <c r="N3" t="b">
         <v>0</v>
       </c>
       <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
+      <c r="P3" s="2" t="n">
+        <v>46174</v>
+      </c>
       <c r="Q3" t="b">
         <v>0</v>
       </c>
       <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
+      <c r="S3" s="2" t="n">
+        <v>46204</v>
+      </c>
       <c r="T3" t="b">
         <v>0</v>
       </c>
       <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
+      <c r="V3" s="2" t="n">
+        <v>46235</v>
+      </c>
       <c r="W3" t="b">
         <v>0</v>
       </c>
       <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="inlineStr"/>
+      <c r="Y3" s="2" t="n">
+        <v>46235</v>
+      </c>
       <c r="Z3" t="b">
         <v>0</v>
       </c>
       <c r="AA3" t="inlineStr"/>
-      <c r="AB3" t="inlineStr"/>
+      <c r="AB3" s="2" t="n">
+        <v>46266</v>
+      </c>
       <c r="AC3" t="b">
         <v>0</v>
       </c>
       <c r="AD3" t="inlineStr"/>
-      <c r="AE3" t="inlineStr"/>
+      <c r="AE3" s="2" t="n">
+        <v>46296</v>
+      </c>
       <c r="AF3" t="b">
         <v>0</v>
       </c>
       <c r="AG3" t="inlineStr"/>
-      <c r="AH3" t="inlineStr"/>
+      <c r="AH3" s="2" t="n">
+        <v>46327</v>
+      </c>
       <c r="AI3" t="b">
         <v>0</v>
       </c>
       <c r="AJ3" t="inlineStr"/>
-      <c r="AK3" t="inlineStr"/>
+      <c r="AK3" s="2" t="n">
+        <v>46357</v>
+      </c>
       <c r="AL3" t="b">
         <v>0</v>
       </c>
       <c r="AM3" t="inlineStr"/>
-      <c r="AN3" t="inlineStr"/>
+      <c r="AN3" s="2" t="n">
+        <v>46388</v>
+      </c>
       <c r="AO3" t="b">
         <v>0</v>
       </c>
       <c r="AP3" t="inlineStr"/>
-      <c r="AQ3" t="inlineStr"/>
+      <c r="AQ3" s="2" t="n">
+        <v>46419</v>
+      </c>
       <c r="AR3" t="b">
         <v>0</v>
       </c>
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="inlineStr"/>
-      <c r="AU3" t="b">
-        <v>0</v>
-      </c>
+      <c r="AU3" t="inlineStr"/>
       <c r="AV3" t="inlineStr"/>
       <c r="AW3" t="inlineStr"/>
-      <c r="AX3" t="b">
-        <v>0</v>
-      </c>
+      <c r="AX3" t="inlineStr"/>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr"/>
-      <c r="BA3" t="b">
-        <v>0</v>
-      </c>
+      <c r="BA3" t="inlineStr"/>
       <c r="BB3" t="inlineStr"/>
       <c r="BC3" t="inlineStr"/>
-      <c r="BD3" t="b">
-        <v>0</v>
-      </c>
+      <c r="BD3" t="inlineStr"/>
       <c r="BE3" t="inlineStr"/>
       <c r="BF3" t="inlineStr"/>
-      <c r="BG3" t="b">
-        <v>0</v>
-      </c>
+      <c r="BG3" t="inlineStr"/>
       <c r="BH3" t="inlineStr"/>
       <c r="BI3" t="inlineStr"/>
-      <c r="BJ3" t="b">
-        <v>0</v>
-      </c>
+      <c r="BJ3" t="inlineStr"/>
       <c r="BK3" t="inlineStr"/>
       <c r="BL3" t="inlineStr"/>
-      <c r="BM3" t="b">
-        <v>0</v>
-      </c>
+      <c r="BM3" t="inlineStr"/>
       <c r="BN3" t="inlineStr"/>
       <c r="BO3" t="inlineStr"/>
-      <c r="BP3" t="b">
-        <v>0</v>
-      </c>
+      <c r="BP3" t="inlineStr"/>
       <c r="BQ3" t="inlineStr"/>
       <c r="BR3" t="inlineStr"/>
-      <c r="BS3" t="b">
-        <v>0</v>
-      </c>
+      <c r="BS3" t="inlineStr"/>
       <c r="BT3" t="inlineStr"/>
       <c r="BU3" t="inlineStr"/>
-      <c r="BV3" t="b">
-        <v>0</v>
-      </c>
+      <c r="BV3" t="inlineStr"/>
       <c r="BW3" t="inlineStr"/>
       <c r="BX3" t="inlineStr"/>
-      <c r="BY3" t="b">
-        <v>0</v>
-      </c>
+      <c r="BY3" t="inlineStr"/>
       <c r="BZ3" t="inlineStr"/>
       <c r="CA3" t="inlineStr"/>
-      <c r="CB3" t="b">
-        <v>0</v>
-      </c>
+      <c r="CB3" t="inlineStr"/>
       <c r="CC3" t="inlineStr"/>
       <c r="CD3" t="inlineStr"/>
-      <c r="CE3" t="b">
-        <v>0</v>
-      </c>
+      <c r="CE3" t="inlineStr"/>
       <c r="CF3" t="inlineStr"/>
       <c r="CG3" t="inlineStr"/>
-      <c r="CH3" t="b">
-        <v>0</v>
-      </c>
+      <c r="CH3" t="inlineStr"/>
       <c r="CI3" t="inlineStr"/>
       <c r="CJ3" t="inlineStr"/>
-      <c r="CK3" t="b">
-        <v>0</v>
-      </c>
+      <c r="CK3" t="inlineStr"/>
       <c r="CL3" t="inlineStr"/>
       <c r="CM3" t="inlineStr"/>
-      <c r="CN3" t="b">
-        <v>0</v>
-      </c>
+      <c r="CN3" t="inlineStr"/>
       <c r="CO3" t="inlineStr"/>
       <c r="CP3" t="inlineStr"/>
-      <c r="CQ3" t="b">
-        <v>0</v>
-      </c>
+      <c r="CQ3" t="inlineStr"/>
       <c r="CR3" t="inlineStr"/>
       <c r="CS3" t="inlineStr"/>
-      <c r="CT3" t="b">
-        <v>0</v>
-      </c>
+      <c r="CT3" t="inlineStr"/>
       <c r="CU3" t="inlineStr"/>
       <c r="CV3" t="inlineStr"/>
-      <c r="CW3" t="b">
-        <v>0</v>
-      </c>
+      <c r="CW3" t="inlineStr"/>
       <c r="CX3" t="inlineStr"/>
       <c r="CY3" t="inlineStr"/>
-      <c r="CZ3" t="b">
-        <v>0</v>
-      </c>
+      <c r="CZ3" t="inlineStr"/>
       <c r="DA3" t="inlineStr"/>
       <c r="DB3" t="inlineStr"/>
-      <c r="DC3" t="b">
-        <v>0</v>
-      </c>
+      <c r="DC3" t="inlineStr"/>
       <c r="DD3" t="inlineStr"/>
       <c r="DE3" t="inlineStr"/>
-      <c r="DF3" t="b">
-        <v>0</v>
-      </c>
+      <c r="DF3" t="inlineStr"/>
       <c r="DG3" t="inlineStr"/>
       <c r="DH3" t="inlineStr"/>
-      <c r="DI3" t="b">
-        <v>0</v>
-      </c>
+      <c r="DI3" t="inlineStr"/>
       <c r="DJ3" t="inlineStr"/>
       <c r="DK3" t="inlineStr"/>
-      <c r="DL3" t="b">
-        <v>0</v>
-      </c>
+      <c r="DL3" t="inlineStr"/>
       <c r="DM3" t="inlineStr"/>
       <c r="DN3" t="inlineStr"/>
-      <c r="DO3" t="b">
-        <v>0</v>
-      </c>
+      <c r="DO3" t="inlineStr"/>
       <c r="DP3" t="inlineStr"/>
       <c r="DQ3" t="inlineStr"/>
-      <c r="DR3" t="b">
-        <v>0</v>
-      </c>
+      <c r="DR3" t="inlineStr"/>
       <c r="DS3" t="inlineStr"/>
       <c r="DT3" t="inlineStr"/>
-      <c r="DU3" t="b">
-        <v>0</v>
-      </c>
+      <c r="DU3" t="inlineStr"/>
       <c r="DV3" t="inlineStr"/>
       <c r="DW3" t="inlineStr"/>
-      <c r="DX3" t="b">
-        <v>0</v>
-      </c>
+      <c r="DX3" t="inlineStr"/>
       <c r="DY3" t="inlineStr"/>
       <c r="DZ3" t="inlineStr"/>
-      <c r="EA3" t="b">
-        <v>0</v>
-      </c>
+      <c r="EA3" t="inlineStr"/>
       <c r="EB3" t="inlineStr"/>
       <c r="EC3" t="inlineStr"/>
-      <c r="ED3" t="b">
-        <v>0</v>
-      </c>
+      <c r="ED3" t="inlineStr"/>
       <c r="EE3" t="inlineStr"/>
       <c r="EF3" t="inlineStr"/>
-      <c r="EG3" t="b">
-        <v>0</v>
-      </c>
+      <c r="EG3" t="inlineStr"/>
       <c r="EH3" t="inlineStr"/>
       <c r="EI3" t="inlineStr"/>
-      <c r="EJ3" t="b">
-        <v>0</v>
-      </c>
+      <c r="EJ3" t="inlineStr"/>
       <c r="EK3" t="inlineStr"/>
       <c r="EL3" t="inlineStr"/>
-      <c r="EM3" t="b">
-        <v>0</v>
-      </c>
+      <c r="EM3" t="inlineStr"/>
       <c r="EN3" t="inlineStr"/>
       <c r="EO3" t="inlineStr"/>
-      <c r="EP3" t="b">
-        <v>0</v>
-      </c>
+      <c r="EP3" t="inlineStr"/>
       <c r="EQ3" t="inlineStr"/>
       <c r="ER3" t="inlineStr"/>
-      <c r="ES3" t="b">
-        <v>0</v>
-      </c>
+      <c r="ES3" t="inlineStr"/>
       <c r="ET3" t="inlineStr"/>
       <c r="EU3" t="inlineStr"/>
-      <c r="EV3" t="b">
-        <v>0</v>
-      </c>
+      <c r="EV3" t="inlineStr"/>
       <c r="EW3" t="inlineStr"/>
       <c r="EX3" t="inlineStr"/>
-      <c r="EY3" t="b">
-        <v>0</v>
-      </c>
+      <c r="EY3" t="inlineStr"/>
       <c r="EZ3" t="inlineStr"/>
       <c r="FA3" t="inlineStr"/>
-      <c r="FB3" t="b">
-        <v>0</v>
-      </c>
+      <c r="FB3" t="inlineStr"/>
       <c r="FC3" t="inlineStr"/>
       <c r="FD3" t="inlineStr"/>
-      <c r="FE3" t="b">
-        <v>0</v>
-      </c>
+      <c r="FE3" t="inlineStr"/>
       <c r="FF3" t="inlineStr"/>
       <c r="FG3" t="inlineStr"/>
-      <c r="FH3" t="b">
-        <v>0</v>
-      </c>
+      <c r="FH3" t="inlineStr"/>
       <c r="FI3" t="inlineStr"/>
       <c r="FJ3" t="inlineStr"/>
-      <c r="FK3" t="b">
-        <v>0</v>
-      </c>
+      <c r="FK3" t="inlineStr"/>
       <c r="FL3" t="inlineStr"/>
       <c r="FM3" t="inlineStr"/>
-      <c r="FN3" t="b">
-        <v>0</v>
-      </c>
+      <c r="FN3" t="inlineStr"/>
       <c r="FO3" t="inlineStr"/>
       <c r="FP3" t="inlineStr"/>
-      <c r="FQ3" t="b">
-        <v>0</v>
-      </c>
+      <c r="FQ3" t="inlineStr"/>
       <c r="FR3" t="inlineStr"/>
       <c r="FS3" t="inlineStr"/>
-      <c r="FT3" t="b">
-        <v>0</v>
-      </c>
+      <c r="FT3" t="inlineStr"/>
       <c r="FU3" t="inlineStr"/>
       <c r="FV3" t="inlineStr"/>
-      <c r="FW3" t="b">
-        <v>0</v>
-      </c>
+      <c r="FW3" t="inlineStr"/>
       <c r="FX3" t="inlineStr"/>
       <c r="FY3" t="inlineStr"/>
-      <c r="FZ3" t="b">
-        <v>0</v>
-      </c>
+      <c r="FZ3" t="inlineStr"/>
       <c r="GA3" t="inlineStr"/>
       <c r="GB3" t="inlineStr"/>
-      <c r="GC3" t="b">
-        <v>0</v>
-      </c>
+      <c r="GC3" t="inlineStr"/>
       <c r="GD3" t="inlineStr"/>
       <c r="GE3" t="inlineStr"/>
-      <c r="GF3" t="b">
-        <v>0</v>
-      </c>
+      <c r="GF3" t="inlineStr"/>
       <c r="GG3" t="inlineStr"/>
     </row>
   </sheetData>

--- a/investors.xlsx
+++ b/investors.xlsx
@@ -16,11 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +49,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:GG3"/>
+  <dimension ref="A1:GG4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1406,9 +1403,13 @@
         <v>46143</v>
       </c>
       <c r="K2" t="b">
-        <v>0</v>
-      </c>
-      <c r="L2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>30-05-2026 08:45:13</t>
+        </is>
+      </c>
       <c r="M2" s="1" t="n">
         <v>46174</v>
       </c>
@@ -1721,12 +1722,10 @@
           <t>Ajay Bhosale</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>9874623097</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="n">
+      <c r="B3" t="n">
+        <v>9874623097</v>
+      </c>
+      <c r="C3" s="1" t="n">
         <v>46082</v>
       </c>
       <c r="D3" t="n">
@@ -1743,90 +1742,98 @@
       <c r="G3" t="n">
         <v>2500000</v>
       </c>
-      <c r="H3" s="2" t="n">
+      <c r="H3" s="1" t="n">
         <v>46508</v>
       </c>
       <c r="I3" t="b">
         <v>0</v>
       </c>
-      <c r="J3" s="2" t="n">
+      <c r="J3" s="1" t="n">
         <v>46113</v>
       </c>
       <c r="K3" t="b">
-        <v>0</v>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>30-05-2026 08:45:51</t>
+        </is>
+      </c>
+      <c r="M3" s="1" t="n">
         <v>46143</v>
       </c>
       <c r="N3" t="b">
-        <v>0</v>
-      </c>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>30-05-2026 08:48:00</t>
+        </is>
+      </c>
+      <c r="P3" s="1" t="n">
         <v>46174</v>
       </c>
       <c r="Q3" t="b">
         <v>0</v>
       </c>
       <c r="R3" t="inlineStr"/>
-      <c r="S3" s="2" t="n">
+      <c r="S3" s="1" t="n">
         <v>46204</v>
       </c>
       <c r="T3" t="b">
         <v>0</v>
       </c>
       <c r="U3" t="inlineStr"/>
-      <c r="V3" s="2" t="n">
+      <c r="V3" s="1" t="n">
         <v>46235</v>
       </c>
       <c r="W3" t="b">
         <v>0</v>
       </c>
       <c r="X3" t="inlineStr"/>
-      <c r="Y3" s="2" t="n">
+      <c r="Y3" s="1" t="n">
         <v>46235</v>
       </c>
       <c r="Z3" t="b">
         <v>0</v>
       </c>
       <c r="AA3" t="inlineStr"/>
-      <c r="AB3" s="2" t="n">
+      <c r="AB3" s="1" t="n">
         <v>46266</v>
       </c>
       <c r="AC3" t="b">
         <v>0</v>
       </c>
       <c r="AD3" t="inlineStr"/>
-      <c r="AE3" s="2" t="n">
+      <c r="AE3" s="1" t="n">
         <v>46296</v>
       </c>
       <c r="AF3" t="b">
         <v>0</v>
       </c>
       <c r="AG3" t="inlineStr"/>
-      <c r="AH3" s="2" t="n">
+      <c r="AH3" s="1" t="n">
         <v>46327</v>
       </c>
       <c r="AI3" t="b">
         <v>0</v>
       </c>
       <c r="AJ3" t="inlineStr"/>
-      <c r="AK3" s="2" t="n">
+      <c r="AK3" s="1" t="n">
         <v>46357</v>
       </c>
       <c r="AL3" t="b">
         <v>0</v>
       </c>
       <c r="AM3" t="inlineStr"/>
-      <c r="AN3" s="2" t="n">
+      <c r="AN3" s="1" t="n">
         <v>46388</v>
       </c>
       <c r="AO3" t="b">
         <v>0</v>
       </c>
       <c r="AP3" t="inlineStr"/>
-      <c r="AQ3" s="2" t="n">
+      <c r="AQ3" s="1" t="n">
         <v>46419</v>
       </c>
       <c r="AR3" t="b">
@@ -1834,149 +1841,590 @@
       </c>
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="inlineStr"/>
-      <c r="AU3" t="inlineStr"/>
+      <c r="AU3" t="b">
+        <v>0</v>
+      </c>
       <c r="AV3" t="inlineStr"/>
       <c r="AW3" t="inlineStr"/>
-      <c r="AX3" t="inlineStr"/>
+      <c r="AX3" t="b">
+        <v>0</v>
+      </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr"/>
-      <c r="BA3" t="inlineStr"/>
+      <c r="BA3" t="b">
+        <v>0</v>
+      </c>
       <c r="BB3" t="inlineStr"/>
       <c r="BC3" t="inlineStr"/>
-      <c r="BD3" t="inlineStr"/>
+      <c r="BD3" t="b">
+        <v>0</v>
+      </c>
       <c r="BE3" t="inlineStr"/>
       <c r="BF3" t="inlineStr"/>
-      <c r="BG3" t="inlineStr"/>
+      <c r="BG3" t="b">
+        <v>0</v>
+      </c>
       <c r="BH3" t="inlineStr"/>
       <c r="BI3" t="inlineStr"/>
-      <c r="BJ3" t="inlineStr"/>
+      <c r="BJ3" t="b">
+        <v>0</v>
+      </c>
       <c r="BK3" t="inlineStr"/>
       <c r="BL3" t="inlineStr"/>
-      <c r="BM3" t="inlineStr"/>
+      <c r="BM3" t="b">
+        <v>0</v>
+      </c>
       <c r="BN3" t="inlineStr"/>
       <c r="BO3" t="inlineStr"/>
-      <c r="BP3" t="inlineStr"/>
+      <c r="BP3" t="b">
+        <v>0</v>
+      </c>
       <c r="BQ3" t="inlineStr"/>
       <c r="BR3" t="inlineStr"/>
-      <c r="BS3" t="inlineStr"/>
+      <c r="BS3" t="b">
+        <v>0</v>
+      </c>
       <c r="BT3" t="inlineStr"/>
       <c r="BU3" t="inlineStr"/>
-      <c r="BV3" t="inlineStr"/>
+      <c r="BV3" t="b">
+        <v>0</v>
+      </c>
       <c r="BW3" t="inlineStr"/>
       <c r="BX3" t="inlineStr"/>
-      <c r="BY3" t="inlineStr"/>
+      <c r="BY3" t="b">
+        <v>0</v>
+      </c>
       <c r="BZ3" t="inlineStr"/>
       <c r="CA3" t="inlineStr"/>
-      <c r="CB3" t="inlineStr"/>
+      <c r="CB3" t="b">
+        <v>0</v>
+      </c>
       <c r="CC3" t="inlineStr"/>
       <c r="CD3" t="inlineStr"/>
-      <c r="CE3" t="inlineStr"/>
+      <c r="CE3" t="b">
+        <v>0</v>
+      </c>
       <c r="CF3" t="inlineStr"/>
       <c r="CG3" t="inlineStr"/>
-      <c r="CH3" t="inlineStr"/>
+      <c r="CH3" t="b">
+        <v>0</v>
+      </c>
       <c r="CI3" t="inlineStr"/>
       <c r="CJ3" t="inlineStr"/>
-      <c r="CK3" t="inlineStr"/>
+      <c r="CK3" t="b">
+        <v>0</v>
+      </c>
       <c r="CL3" t="inlineStr"/>
       <c r="CM3" t="inlineStr"/>
-      <c r="CN3" t="inlineStr"/>
+      <c r="CN3" t="b">
+        <v>0</v>
+      </c>
       <c r="CO3" t="inlineStr"/>
       <c r="CP3" t="inlineStr"/>
-      <c r="CQ3" t="inlineStr"/>
+      <c r="CQ3" t="b">
+        <v>0</v>
+      </c>
       <c r="CR3" t="inlineStr"/>
       <c r="CS3" t="inlineStr"/>
-      <c r="CT3" t="inlineStr"/>
+      <c r="CT3" t="b">
+        <v>0</v>
+      </c>
       <c r="CU3" t="inlineStr"/>
       <c r="CV3" t="inlineStr"/>
-      <c r="CW3" t="inlineStr"/>
+      <c r="CW3" t="b">
+        <v>0</v>
+      </c>
       <c r="CX3" t="inlineStr"/>
       <c r="CY3" t="inlineStr"/>
-      <c r="CZ3" t="inlineStr"/>
+      <c r="CZ3" t="b">
+        <v>0</v>
+      </c>
       <c r="DA3" t="inlineStr"/>
       <c r="DB3" t="inlineStr"/>
-      <c r="DC3" t="inlineStr"/>
+      <c r="DC3" t="b">
+        <v>0</v>
+      </c>
       <c r="DD3" t="inlineStr"/>
       <c r="DE3" t="inlineStr"/>
-      <c r="DF3" t="inlineStr"/>
+      <c r="DF3" t="b">
+        <v>0</v>
+      </c>
       <c r="DG3" t="inlineStr"/>
       <c r="DH3" t="inlineStr"/>
-      <c r="DI3" t="inlineStr"/>
+      <c r="DI3" t="b">
+        <v>0</v>
+      </c>
       <c r="DJ3" t="inlineStr"/>
       <c r="DK3" t="inlineStr"/>
-      <c r="DL3" t="inlineStr"/>
+      <c r="DL3" t="b">
+        <v>0</v>
+      </c>
       <c r="DM3" t="inlineStr"/>
       <c r="DN3" t="inlineStr"/>
-      <c r="DO3" t="inlineStr"/>
+      <c r="DO3" t="b">
+        <v>0</v>
+      </c>
       <c r="DP3" t="inlineStr"/>
       <c r="DQ3" t="inlineStr"/>
-      <c r="DR3" t="inlineStr"/>
+      <c r="DR3" t="b">
+        <v>0</v>
+      </c>
       <c r="DS3" t="inlineStr"/>
       <c r="DT3" t="inlineStr"/>
-      <c r="DU3" t="inlineStr"/>
+      <c r="DU3" t="b">
+        <v>0</v>
+      </c>
       <c r="DV3" t="inlineStr"/>
       <c r="DW3" t="inlineStr"/>
-      <c r="DX3" t="inlineStr"/>
+      <c r="DX3" t="b">
+        <v>0</v>
+      </c>
       <c r="DY3" t="inlineStr"/>
       <c r="DZ3" t="inlineStr"/>
-      <c r="EA3" t="inlineStr"/>
+      <c r="EA3" t="b">
+        <v>0</v>
+      </c>
       <c r="EB3" t="inlineStr"/>
       <c r="EC3" t="inlineStr"/>
-      <c r="ED3" t="inlineStr"/>
+      <c r="ED3" t="b">
+        <v>0</v>
+      </c>
       <c r="EE3" t="inlineStr"/>
       <c r="EF3" t="inlineStr"/>
-      <c r="EG3" t="inlineStr"/>
+      <c r="EG3" t="b">
+        <v>0</v>
+      </c>
       <c r="EH3" t="inlineStr"/>
       <c r="EI3" t="inlineStr"/>
-      <c r="EJ3" t="inlineStr"/>
+      <c r="EJ3" t="b">
+        <v>0</v>
+      </c>
       <c r="EK3" t="inlineStr"/>
       <c r="EL3" t="inlineStr"/>
-      <c r="EM3" t="inlineStr"/>
+      <c r="EM3" t="b">
+        <v>0</v>
+      </c>
       <c r="EN3" t="inlineStr"/>
       <c r="EO3" t="inlineStr"/>
-      <c r="EP3" t="inlineStr"/>
+      <c r="EP3" t="b">
+        <v>0</v>
+      </c>
       <c r="EQ3" t="inlineStr"/>
       <c r="ER3" t="inlineStr"/>
-      <c r="ES3" t="inlineStr"/>
+      <c r="ES3" t="b">
+        <v>0</v>
+      </c>
       <c r="ET3" t="inlineStr"/>
       <c r="EU3" t="inlineStr"/>
-      <c r="EV3" t="inlineStr"/>
+      <c r="EV3" t="b">
+        <v>0</v>
+      </c>
       <c r="EW3" t="inlineStr"/>
       <c r="EX3" t="inlineStr"/>
-      <c r="EY3" t="inlineStr"/>
+      <c r="EY3" t="b">
+        <v>0</v>
+      </c>
       <c r="EZ3" t="inlineStr"/>
       <c r="FA3" t="inlineStr"/>
-      <c r="FB3" t="inlineStr"/>
+      <c r="FB3" t="b">
+        <v>0</v>
+      </c>
       <c r="FC3" t="inlineStr"/>
       <c r="FD3" t="inlineStr"/>
-      <c r="FE3" t="inlineStr"/>
+      <c r="FE3" t="b">
+        <v>0</v>
+      </c>
       <c r="FF3" t="inlineStr"/>
       <c r="FG3" t="inlineStr"/>
-      <c r="FH3" t="inlineStr"/>
+      <c r="FH3" t="b">
+        <v>0</v>
+      </c>
       <c r="FI3" t="inlineStr"/>
       <c r="FJ3" t="inlineStr"/>
-      <c r="FK3" t="inlineStr"/>
+      <c r="FK3" t="b">
+        <v>0</v>
+      </c>
       <c r="FL3" t="inlineStr"/>
       <c r="FM3" t="inlineStr"/>
-      <c r="FN3" t="inlineStr"/>
+      <c r="FN3" t="b">
+        <v>0</v>
+      </c>
       <c r="FO3" t="inlineStr"/>
       <c r="FP3" t="inlineStr"/>
-      <c r="FQ3" t="inlineStr"/>
+      <c r="FQ3" t="b">
+        <v>0</v>
+      </c>
       <c r="FR3" t="inlineStr"/>
       <c r="FS3" t="inlineStr"/>
-      <c r="FT3" t="inlineStr"/>
+      <c r="FT3" t="b">
+        <v>0</v>
+      </c>
       <c r="FU3" t="inlineStr"/>
       <c r="FV3" t="inlineStr"/>
-      <c r="FW3" t="inlineStr"/>
+      <c r="FW3" t="b">
+        <v>0</v>
+      </c>
       <c r="FX3" t="inlineStr"/>
       <c r="FY3" t="inlineStr"/>
-      <c r="FZ3" t="inlineStr"/>
+      <c r="FZ3" t="b">
+        <v>0</v>
+      </c>
       <c r="GA3" t="inlineStr"/>
       <c r="GB3" t="inlineStr"/>
-      <c r="GC3" t="inlineStr"/>
+      <c r="GC3" t="b">
+        <v>0</v>
+      </c>
       <c r="GD3" t="inlineStr"/>
       <c r="GE3" t="inlineStr"/>
-      <c r="GF3" t="inlineStr"/>
+      <c r="GF3" t="b">
+        <v>0</v>
+      </c>
       <c r="GG3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Santosh Pawar</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>87238949823784</v>
+      </c>
+      <c r="C4" s="1" t="n">
+        <v>46169</v>
+      </c>
+      <c r="D4" t="n">
+        <v>100000</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>JmD 1.0</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G4" t="n">
+        <v>50000</v>
+      </c>
+      <c r="H4" s="1" t="n">
+        <v>46169</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" s="1" t="n">
+        <v>46508</v>
+      </c>
+      <c r="K4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>27-05-2026 18:45:46</t>
+        </is>
+      </c>
+      <c r="M4" s="1" t="n">
+        <v>46169</v>
+      </c>
+      <c r="N4" t="b">
+        <v>1</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>27-05-2026 18:44:27</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="b">
+        <v>0</v>
+      </c>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="b">
+        <v>0</v>
+      </c>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="b">
+        <v>0</v>
+      </c>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr"/>
+      <c r="AF4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr"/>
+      <c r="AI4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr"/>
+      <c r="AK4" t="inlineStr"/>
+      <c r="AL4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM4" t="inlineStr"/>
+      <c r="AN4" t="inlineStr"/>
+      <c r="AO4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP4" t="inlineStr"/>
+      <c r="AQ4" t="inlineStr"/>
+      <c r="AR4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS4" t="inlineStr"/>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AU4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AV4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr"/>
+      <c r="AX4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr"/>
+      <c r="BA4" t="b">
+        <v>0</v>
+      </c>
+      <c r="BB4" t="inlineStr"/>
+      <c r="BC4" t="inlineStr"/>
+      <c r="BD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="BE4" t="inlineStr"/>
+      <c r="BF4" t="inlineStr"/>
+      <c r="BG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="BH4" t="inlineStr"/>
+      <c r="BI4" t="inlineStr"/>
+      <c r="BJ4" t="b">
+        <v>0</v>
+      </c>
+      <c r="BK4" t="inlineStr"/>
+      <c r="BL4" t="inlineStr"/>
+      <c r="BM4" t="b">
+        <v>0</v>
+      </c>
+      <c r="BN4" t="inlineStr"/>
+      <c r="BO4" t="inlineStr"/>
+      <c r="BP4" t="b">
+        <v>0</v>
+      </c>
+      <c r="BQ4" t="inlineStr"/>
+      <c r="BR4" t="inlineStr"/>
+      <c r="BS4" t="b">
+        <v>0</v>
+      </c>
+      <c r="BT4" t="inlineStr"/>
+      <c r="BU4" t="inlineStr"/>
+      <c r="BV4" t="b">
+        <v>0</v>
+      </c>
+      <c r="BW4" t="inlineStr"/>
+      <c r="BX4" t="inlineStr"/>
+      <c r="BY4" t="b">
+        <v>0</v>
+      </c>
+      <c r="BZ4" t="inlineStr"/>
+      <c r="CA4" t="inlineStr"/>
+      <c r="CB4" t="b">
+        <v>0</v>
+      </c>
+      <c r="CC4" t="inlineStr"/>
+      <c r="CD4" t="inlineStr"/>
+      <c r="CE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="CF4" t="inlineStr"/>
+      <c r="CG4" t="inlineStr"/>
+      <c r="CH4" t="b">
+        <v>0</v>
+      </c>
+      <c r="CI4" t="inlineStr"/>
+      <c r="CJ4" t="inlineStr"/>
+      <c r="CK4" t="b">
+        <v>0</v>
+      </c>
+      <c r="CL4" t="inlineStr"/>
+      <c r="CM4" t="inlineStr"/>
+      <c r="CN4" t="b">
+        <v>0</v>
+      </c>
+      <c r="CO4" t="inlineStr"/>
+      <c r="CP4" t="inlineStr"/>
+      <c r="CQ4" t="b">
+        <v>0</v>
+      </c>
+      <c r="CR4" t="inlineStr"/>
+      <c r="CS4" t="inlineStr"/>
+      <c r="CT4" t="b">
+        <v>0</v>
+      </c>
+      <c r="CU4" t="inlineStr"/>
+      <c r="CV4" t="inlineStr"/>
+      <c r="CW4" t="b">
+        <v>0</v>
+      </c>
+      <c r="CX4" t="inlineStr"/>
+      <c r="CY4" t="inlineStr"/>
+      <c r="CZ4" t="b">
+        <v>0</v>
+      </c>
+      <c r="DA4" t="inlineStr"/>
+      <c r="DB4" t="inlineStr"/>
+      <c r="DC4" t="b">
+        <v>0</v>
+      </c>
+      <c r="DD4" t="inlineStr"/>
+      <c r="DE4" t="inlineStr"/>
+      <c r="DF4" t="b">
+        <v>0</v>
+      </c>
+      <c r="DG4" t="inlineStr"/>
+      <c r="DH4" t="inlineStr"/>
+      <c r="DI4" t="b">
+        <v>0</v>
+      </c>
+      <c r="DJ4" t="inlineStr"/>
+      <c r="DK4" t="inlineStr"/>
+      <c r="DL4" t="b">
+        <v>0</v>
+      </c>
+      <c r="DM4" t="inlineStr"/>
+      <c r="DN4" t="inlineStr"/>
+      <c r="DO4" t="b">
+        <v>0</v>
+      </c>
+      <c r="DP4" t="inlineStr"/>
+      <c r="DQ4" t="inlineStr"/>
+      <c r="DR4" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS4" t="inlineStr"/>
+      <c r="DT4" t="inlineStr"/>
+      <c r="DU4" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV4" t="inlineStr"/>
+      <c r="DW4" t="inlineStr"/>
+      <c r="DX4" t="b">
+        <v>0</v>
+      </c>
+      <c r="DY4" t="inlineStr"/>
+      <c r="DZ4" t="inlineStr"/>
+      <c r="EA4" t="b">
+        <v>0</v>
+      </c>
+      <c r="EB4" t="inlineStr"/>
+      <c r="EC4" t="inlineStr"/>
+      <c r="ED4" t="b">
+        <v>0</v>
+      </c>
+      <c r="EE4" t="inlineStr"/>
+      <c r="EF4" t="inlineStr"/>
+      <c r="EG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="EH4" t="inlineStr"/>
+      <c r="EI4" t="inlineStr"/>
+      <c r="EJ4" t="b">
+        <v>0</v>
+      </c>
+      <c r="EK4" t="inlineStr"/>
+      <c r="EL4" t="inlineStr"/>
+      <c r="EM4" t="b">
+        <v>0</v>
+      </c>
+      <c r="EN4" t="inlineStr"/>
+      <c r="EO4" t="inlineStr"/>
+      <c r="EP4" t="b">
+        <v>0</v>
+      </c>
+      <c r="EQ4" t="inlineStr"/>
+      <c r="ER4" t="inlineStr"/>
+      <c r="ES4" t="b">
+        <v>0</v>
+      </c>
+      <c r="ET4" t="inlineStr"/>
+      <c r="EU4" t="inlineStr"/>
+      <c r="EV4" t="b">
+        <v>0</v>
+      </c>
+      <c r="EW4" t="inlineStr"/>
+      <c r="EX4" t="inlineStr"/>
+      <c r="EY4" t="b">
+        <v>0</v>
+      </c>
+      <c r="EZ4" t="inlineStr"/>
+      <c r="FA4" t="inlineStr"/>
+      <c r="FB4" t="b">
+        <v>0</v>
+      </c>
+      <c r="FC4" t="inlineStr"/>
+      <c r="FD4" t="inlineStr"/>
+      <c r="FE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="FF4" t="inlineStr"/>
+      <c r="FG4" t="inlineStr"/>
+      <c r="FH4" t="b">
+        <v>0</v>
+      </c>
+      <c r="FI4" t="inlineStr"/>
+      <c r="FJ4" t="inlineStr"/>
+      <c r="FK4" t="b">
+        <v>0</v>
+      </c>
+      <c r="FL4" t="inlineStr"/>
+      <c r="FM4" t="inlineStr"/>
+      <c r="FN4" t="b">
+        <v>0</v>
+      </c>
+      <c r="FO4" t="inlineStr"/>
+      <c r="FP4" t="inlineStr"/>
+      <c r="FQ4" t="b">
+        <v>0</v>
+      </c>
+      <c r="FR4" t="inlineStr"/>
+      <c r="FS4" t="inlineStr"/>
+      <c r="FT4" t="b">
+        <v>0</v>
+      </c>
+      <c r="FU4" t="inlineStr"/>
+      <c r="FV4" t="inlineStr"/>
+      <c r="FW4" t="b">
+        <v>0</v>
+      </c>
+      <c r="FX4" t="inlineStr"/>
+      <c r="FY4" t="inlineStr"/>
+      <c r="FZ4" t="b">
+        <v>0</v>
+      </c>
+      <c r="GA4" t="inlineStr"/>
+      <c r="GB4" t="inlineStr"/>
+      <c r="GC4" t="b">
+        <v>0</v>
+      </c>
+      <c r="GD4" t="inlineStr"/>
+      <c r="GE4" t="inlineStr"/>
+      <c r="GF4" t="b">
+        <v>0</v>
+      </c>
+      <c r="GG4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/investors.xlsx
+++ b/investors.xlsx
@@ -16,9 +16,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -49,9 +51,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:GG4"/>
+  <dimension ref="A1:GT5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,910 +461,975 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
+          <t>PROFIT PERCENTAGE</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>CAPITAL RETURN</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>CAPITAL_PAID</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>REFERRAL NAME</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>REFERRAL AMOUNT</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>REFERRAL_PAID</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>PAYOUT TYPE</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>NUMBER OF PAYOUTS</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>BANK NAME</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>ACCOUNT HOLDER NAME</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>ACCOUNT NUMBER</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>IFSC CODE</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>BRANCH NAME</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>PAN NUMBER</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>AADHAAR NUMBER</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
         <is>
           <t>PROFIT DATE 1</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>PAID_1</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>PAYMENT_DATE_1</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>PROFIT DATE 2</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>PAID_2</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>PAYMENT_DATE_2</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>PROFIT DATE 3</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>PAID_3</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>PAYMENT_DATE_3</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>PROFIT DATE 4</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>PAID_4</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>PAYMENT_DATE_4</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>PROFIT DATE 5</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>PAID_5</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>PAYMENT_DATE_5</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>PROFIT DATE 6</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>PAID_6</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>PAYMENT_DATE_6</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>PROFIT DATE 7</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>PAID_7</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>PAYMENT_DATE_7</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>PROFIT DATE 8</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>PAID_8</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>PAYMENT_DATE_8</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>PROFIT DATE 9</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>PAID_9</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>PAYMENT_DATE_9</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>PROFIT DATE 10</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>PAID_10</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>PAYMENT_DATE_10</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>PROFIT DATE 11</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>PAID_11</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="BC1" t="inlineStr">
         <is>
           <t>PAYMENT_DATE_11</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="BD1" t="inlineStr">
         <is>
           <t>PROFIT DATE 12</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="BE1" t="inlineStr">
         <is>
           <t>PAID_12</t>
         </is>
       </c>
-      <c r="AS1" t="inlineStr">
+      <c r="BF1" t="inlineStr">
         <is>
           <t>PAYMENT_DATE_12</t>
         </is>
       </c>
-      <c r="AT1" t="inlineStr">
+      <c r="BG1" t="inlineStr">
         <is>
           <t>PROFIT DATE 13</t>
         </is>
       </c>
-      <c r="AU1" t="inlineStr">
+      <c r="BH1" t="inlineStr">
         <is>
           <t>PAID_13</t>
         </is>
       </c>
-      <c r="AV1" t="inlineStr">
+      <c r="BI1" t="inlineStr">
         <is>
           <t>PAYMENT_DATE_13</t>
         </is>
       </c>
-      <c r="AW1" t="inlineStr">
+      <c r="BJ1" t="inlineStr">
         <is>
           <t>PROFIT DATE 14</t>
         </is>
       </c>
-      <c r="AX1" t="inlineStr">
+      <c r="BK1" t="inlineStr">
         <is>
           <t>PAID_14</t>
         </is>
       </c>
-      <c r="AY1" t="inlineStr">
+      <c r="BL1" t="inlineStr">
         <is>
           <t>PAYMENT_DATE_14</t>
         </is>
       </c>
-      <c r="AZ1" t="inlineStr">
+      <c r="BM1" t="inlineStr">
         <is>
           <t>PROFIT DATE 15</t>
         </is>
       </c>
-      <c r="BA1" t="inlineStr">
+      <c r="BN1" t="inlineStr">
         <is>
           <t>PAID_15</t>
         </is>
       </c>
-      <c r="BB1" t="inlineStr">
+      <c r="BO1" t="inlineStr">
         <is>
           <t>PAYMENT_DATE_15</t>
         </is>
       </c>
-      <c r="BC1" t="inlineStr">
+      <c r="BP1" t="inlineStr">
         <is>
           <t>PROFIT DATE 16</t>
         </is>
       </c>
-      <c r="BD1" t="inlineStr">
+      <c r="BQ1" t="inlineStr">
         <is>
           <t>PAID_16</t>
         </is>
       </c>
-      <c r="BE1" t="inlineStr">
+      <c r="BR1" t="inlineStr">
         <is>
           <t>PAYMENT_DATE_16</t>
         </is>
       </c>
-      <c r="BF1" t="inlineStr">
+      <c r="BS1" t="inlineStr">
         <is>
           <t>PROFIT DATE 17</t>
         </is>
       </c>
-      <c r="BG1" t="inlineStr">
+      <c r="BT1" t="inlineStr">
         <is>
           <t>PAID_17</t>
         </is>
       </c>
-      <c r="BH1" t="inlineStr">
+      <c r="BU1" t="inlineStr">
         <is>
           <t>PAYMENT_DATE_17</t>
         </is>
       </c>
-      <c r="BI1" t="inlineStr">
+      <c r="BV1" t="inlineStr">
         <is>
           <t>PROFIT DATE 18</t>
         </is>
       </c>
-      <c r="BJ1" t="inlineStr">
+      <c r="BW1" t="inlineStr">
         <is>
           <t>PAID_18</t>
         </is>
       </c>
-      <c r="BK1" t="inlineStr">
+      <c r="BX1" t="inlineStr">
         <is>
           <t>PAYMENT_DATE_18</t>
         </is>
       </c>
-      <c r="BL1" t="inlineStr">
+      <c r="BY1" t="inlineStr">
         <is>
           <t>PROFIT DATE 19</t>
         </is>
       </c>
-      <c r="BM1" t="inlineStr">
+      <c r="BZ1" t="inlineStr">
         <is>
           <t>PAID_19</t>
         </is>
       </c>
-      <c r="BN1" t="inlineStr">
+      <c r="CA1" t="inlineStr">
         <is>
           <t>PAYMENT_DATE_19</t>
         </is>
       </c>
-      <c r="BO1" t="inlineStr">
+      <c r="CB1" t="inlineStr">
         <is>
           <t>PROFIT DATE 20</t>
         </is>
       </c>
-      <c r="BP1" t="inlineStr">
+      <c r="CC1" t="inlineStr">
         <is>
           <t>PAID_20</t>
         </is>
       </c>
-      <c r="BQ1" t="inlineStr">
+      <c r="CD1" t="inlineStr">
         <is>
           <t>PAYMENT_DATE_20</t>
         </is>
       </c>
-      <c r="BR1" t="inlineStr">
+      <c r="CE1" t="inlineStr">
         <is>
           <t>PROFIT DATE 21</t>
         </is>
       </c>
-      <c r="BS1" t="inlineStr">
+      <c r="CF1" t="inlineStr">
         <is>
           <t>PAID_21</t>
         </is>
       </c>
-      <c r="BT1" t="inlineStr">
+      <c r="CG1" t="inlineStr">
         <is>
           <t>PAYMENT_DATE_21</t>
         </is>
       </c>
-      <c r="BU1" t="inlineStr">
+      <c r="CH1" t="inlineStr">
         <is>
           <t>PROFIT DATE 22</t>
         </is>
       </c>
-      <c r="BV1" t="inlineStr">
+      <c r="CI1" t="inlineStr">
         <is>
           <t>PAID_22</t>
         </is>
       </c>
-      <c r="BW1" t="inlineStr">
+      <c r="CJ1" t="inlineStr">
         <is>
           <t>PAYMENT_DATE_22</t>
         </is>
       </c>
-      <c r="BX1" t="inlineStr">
+      <c r="CK1" t="inlineStr">
         <is>
           <t>PROFIT DATE 23</t>
         </is>
       </c>
-      <c r="BY1" t="inlineStr">
+      <c r="CL1" t="inlineStr">
         <is>
           <t>PAID_23</t>
         </is>
       </c>
-      <c r="BZ1" t="inlineStr">
+      <c r="CM1" t="inlineStr">
         <is>
           <t>PAYMENT_DATE_23</t>
         </is>
       </c>
-      <c r="CA1" t="inlineStr">
+      <c r="CN1" t="inlineStr">
         <is>
           <t>PROFIT DATE 24</t>
         </is>
       </c>
-      <c r="CB1" t="inlineStr">
+      <c r="CO1" t="inlineStr">
         <is>
           <t>PAID_24</t>
         </is>
       </c>
-      <c r="CC1" t="inlineStr">
+      <c r="CP1" t="inlineStr">
         <is>
           <t>PAYMENT_DATE_24</t>
         </is>
       </c>
-      <c r="CD1" t="inlineStr">
+      <c r="CQ1" t="inlineStr">
         <is>
           <t>PROFIT DATE 25</t>
         </is>
       </c>
-      <c r="CE1" t="inlineStr">
+      <c r="CR1" t="inlineStr">
         <is>
           <t>PAID_25</t>
         </is>
       </c>
-      <c r="CF1" t="inlineStr">
+      <c r="CS1" t="inlineStr">
         <is>
           <t>PAYMENT_DATE_25</t>
         </is>
       </c>
-      <c r="CG1" t="inlineStr">
+      <c r="CT1" t="inlineStr">
         <is>
           <t>PROFIT DATE 26</t>
         </is>
       </c>
-      <c r="CH1" t="inlineStr">
+      <c r="CU1" t="inlineStr">
         <is>
           <t>PAID_26</t>
         </is>
       </c>
-      <c r="CI1" t="inlineStr">
+      <c r="CV1" t="inlineStr">
         <is>
           <t>PAYMENT_DATE_26</t>
         </is>
       </c>
-      <c r="CJ1" t="inlineStr">
+      <c r="CW1" t="inlineStr">
         <is>
           <t>PROFIT DATE 27</t>
         </is>
       </c>
-      <c r="CK1" t="inlineStr">
+      <c r="CX1" t="inlineStr">
         <is>
           <t>PAID_27</t>
         </is>
       </c>
-      <c r="CL1" t="inlineStr">
+      <c r="CY1" t="inlineStr">
         <is>
           <t>PAYMENT_DATE_27</t>
         </is>
       </c>
-      <c r="CM1" t="inlineStr">
+      <c r="CZ1" t="inlineStr">
         <is>
           <t>PROFIT DATE 28</t>
         </is>
       </c>
-      <c r="CN1" t="inlineStr">
+      <c r="DA1" t="inlineStr">
         <is>
           <t>PAID_28</t>
         </is>
       </c>
-      <c r="CO1" t="inlineStr">
+      <c r="DB1" t="inlineStr">
         <is>
           <t>PAYMENT_DATE_28</t>
         </is>
       </c>
-      <c r="CP1" t="inlineStr">
+      <c r="DC1" t="inlineStr">
         <is>
           <t>PROFIT DATE 29</t>
         </is>
       </c>
-      <c r="CQ1" t="inlineStr">
+      <c r="DD1" t="inlineStr">
         <is>
           <t>PAID_29</t>
         </is>
       </c>
-      <c r="CR1" t="inlineStr">
+      <c r="DE1" t="inlineStr">
         <is>
           <t>PAYMENT_DATE_29</t>
         </is>
       </c>
-      <c r="CS1" t="inlineStr">
+      <c r="DF1" t="inlineStr">
         <is>
           <t>PROFIT DATE 30</t>
         </is>
       </c>
-      <c r="CT1" t="inlineStr">
+      <c r="DG1" t="inlineStr">
         <is>
           <t>PAID_30</t>
         </is>
       </c>
-      <c r="CU1" t="inlineStr">
+      <c r="DH1" t="inlineStr">
         <is>
           <t>PAYMENT_DATE_30</t>
         </is>
       </c>
-      <c r="CV1" t="inlineStr">
+      <c r="DI1" t="inlineStr">
         <is>
           <t>PROFIT DATE 31</t>
         </is>
       </c>
-      <c r="CW1" t="inlineStr">
+      <c r="DJ1" t="inlineStr">
         <is>
           <t>PAID_31</t>
         </is>
       </c>
-      <c r="CX1" t="inlineStr">
+      <c r="DK1" t="inlineStr">
         <is>
           <t>PAYMENT_DATE_31</t>
         </is>
       </c>
-      <c r="CY1" t="inlineStr">
+      <c r="DL1" t="inlineStr">
         <is>
           <t>PROFIT DATE 32</t>
         </is>
       </c>
-      <c r="CZ1" t="inlineStr">
+      <c r="DM1" t="inlineStr">
         <is>
           <t>PAID_32</t>
         </is>
       </c>
-      <c r="DA1" t="inlineStr">
+      <c r="DN1" t="inlineStr">
         <is>
           <t>PAYMENT_DATE_32</t>
         </is>
       </c>
-      <c r="DB1" t="inlineStr">
+      <c r="DO1" t="inlineStr">
         <is>
           <t>PROFIT DATE 33</t>
         </is>
       </c>
-      <c r="DC1" t="inlineStr">
+      <c r="DP1" t="inlineStr">
         <is>
           <t>PAID_33</t>
         </is>
       </c>
-      <c r="DD1" t="inlineStr">
+      <c r="DQ1" t="inlineStr">
         <is>
           <t>PAYMENT_DATE_33</t>
         </is>
       </c>
-      <c r="DE1" t="inlineStr">
+      <c r="DR1" t="inlineStr">
         <is>
           <t>PROFIT DATE 34</t>
         </is>
       </c>
-      <c r="DF1" t="inlineStr">
+      <c r="DS1" t="inlineStr">
         <is>
           <t>PAID_34</t>
         </is>
       </c>
-      <c r="DG1" t="inlineStr">
+      <c r="DT1" t="inlineStr">
         <is>
           <t>PAYMENT_DATE_34</t>
         </is>
       </c>
-      <c r="DH1" t="inlineStr">
+      <c r="DU1" t="inlineStr">
         <is>
           <t>PROFIT DATE 35</t>
         </is>
       </c>
-      <c r="DI1" t="inlineStr">
+      <c r="DV1" t="inlineStr">
         <is>
           <t>PAID_35</t>
         </is>
       </c>
-      <c r="DJ1" t="inlineStr">
+      <c r="DW1" t="inlineStr">
         <is>
           <t>PAYMENT_DATE_35</t>
         </is>
       </c>
-      <c r="DK1" t="inlineStr">
+      <c r="DX1" t="inlineStr">
         <is>
           <t>PROFIT DATE 36</t>
         </is>
       </c>
-      <c r="DL1" t="inlineStr">
+      <c r="DY1" t="inlineStr">
         <is>
           <t>PAID_36</t>
         </is>
       </c>
-      <c r="DM1" t="inlineStr">
+      <c r="DZ1" t="inlineStr">
         <is>
           <t>PAYMENT_DATE_36</t>
         </is>
       </c>
-      <c r="DN1" t="inlineStr">
+      <c r="EA1" t="inlineStr">
         <is>
           <t>PROFIT DATE 37</t>
         </is>
       </c>
-      <c r="DO1" t="inlineStr">
+      <c r="EB1" t="inlineStr">
         <is>
           <t>PAID_37</t>
         </is>
       </c>
-      <c r="DP1" t="inlineStr">
+      <c r="EC1" t="inlineStr">
         <is>
           <t>PAYMENT_DATE_37</t>
         </is>
       </c>
-      <c r="DQ1" t="inlineStr">
+      <c r="ED1" t="inlineStr">
         <is>
           <t>PROFIT DATE 38</t>
         </is>
       </c>
-      <c r="DR1" t="inlineStr">
+      <c r="EE1" t="inlineStr">
         <is>
           <t>PAID_38</t>
         </is>
       </c>
-      <c r="DS1" t="inlineStr">
+      <c r="EF1" t="inlineStr">
         <is>
           <t>PAYMENT_DATE_38</t>
         </is>
       </c>
-      <c r="DT1" t="inlineStr">
+      <c r="EG1" t="inlineStr">
         <is>
           <t>PROFIT DATE 39</t>
         </is>
       </c>
-      <c r="DU1" t="inlineStr">
+      <c r="EH1" t="inlineStr">
         <is>
           <t>PAID_39</t>
         </is>
       </c>
-      <c r="DV1" t="inlineStr">
+      <c r="EI1" t="inlineStr">
         <is>
           <t>PAYMENT_DATE_39</t>
         </is>
       </c>
-      <c r="DW1" t="inlineStr">
+      <c r="EJ1" t="inlineStr">
         <is>
           <t>PROFIT DATE 40</t>
         </is>
       </c>
-      <c r="DX1" t="inlineStr">
+      <c r="EK1" t="inlineStr">
         <is>
           <t>PAID_40</t>
         </is>
       </c>
-      <c r="DY1" t="inlineStr">
+      <c r="EL1" t="inlineStr">
         <is>
           <t>PAYMENT_DATE_40</t>
         </is>
       </c>
-      <c r="DZ1" t="inlineStr">
+      <c r="EM1" t="inlineStr">
         <is>
           <t>PROFIT DATE 41</t>
         </is>
       </c>
-      <c r="EA1" t="inlineStr">
+      <c r="EN1" t="inlineStr">
         <is>
           <t>PAID_41</t>
         </is>
       </c>
-      <c r="EB1" t="inlineStr">
+      <c r="EO1" t="inlineStr">
         <is>
           <t>PAYMENT_DATE_41</t>
         </is>
       </c>
-      <c r="EC1" t="inlineStr">
+      <c r="EP1" t="inlineStr">
         <is>
           <t>PROFIT DATE 42</t>
         </is>
       </c>
-      <c r="ED1" t="inlineStr">
+      <c r="EQ1" t="inlineStr">
         <is>
           <t>PAID_42</t>
         </is>
       </c>
-      <c r="EE1" t="inlineStr">
+      <c r="ER1" t="inlineStr">
         <is>
           <t>PAYMENT_DATE_42</t>
         </is>
       </c>
-      <c r="EF1" t="inlineStr">
+      <c r="ES1" t="inlineStr">
         <is>
           <t>PROFIT DATE 43</t>
         </is>
       </c>
-      <c r="EG1" t="inlineStr">
+      <c r="ET1" t="inlineStr">
         <is>
           <t>PAID_43</t>
         </is>
       </c>
-      <c r="EH1" t="inlineStr">
+      <c r="EU1" t="inlineStr">
         <is>
           <t>PAYMENT_DATE_43</t>
         </is>
       </c>
-      <c r="EI1" t="inlineStr">
+      <c r="EV1" t="inlineStr">
         <is>
           <t>PROFIT DATE 44</t>
         </is>
       </c>
-      <c r="EJ1" t="inlineStr">
+      <c r="EW1" t="inlineStr">
         <is>
           <t>PAID_44</t>
         </is>
       </c>
-      <c r="EK1" t="inlineStr">
+      <c r="EX1" t="inlineStr">
         <is>
           <t>PAYMENT_DATE_44</t>
         </is>
       </c>
-      <c r="EL1" t="inlineStr">
+      <c r="EY1" t="inlineStr">
         <is>
           <t>PROFIT DATE 45</t>
         </is>
       </c>
-      <c r="EM1" t="inlineStr">
+      <c r="EZ1" t="inlineStr">
         <is>
           <t>PAID_45</t>
         </is>
       </c>
-      <c r="EN1" t="inlineStr">
+      <c r="FA1" t="inlineStr">
         <is>
           <t>PAYMENT_DATE_45</t>
         </is>
       </c>
-      <c r="EO1" t="inlineStr">
+      <c r="FB1" t="inlineStr">
         <is>
           <t>PROFIT DATE 46</t>
         </is>
       </c>
-      <c r="EP1" t="inlineStr">
+      <c r="FC1" t="inlineStr">
         <is>
           <t>PAID_46</t>
         </is>
       </c>
-      <c r="EQ1" t="inlineStr">
+      <c r="FD1" t="inlineStr">
         <is>
           <t>PAYMENT_DATE_46</t>
         </is>
       </c>
-      <c r="ER1" t="inlineStr">
+      <c r="FE1" t="inlineStr">
         <is>
           <t>PROFIT DATE 47</t>
         </is>
       </c>
-      <c r="ES1" t="inlineStr">
+      <c r="FF1" t="inlineStr">
         <is>
           <t>PAID_47</t>
         </is>
       </c>
-      <c r="ET1" t="inlineStr">
+      <c r="FG1" t="inlineStr">
         <is>
           <t>PAYMENT_DATE_47</t>
         </is>
       </c>
-      <c r="EU1" t="inlineStr">
+      <c r="FH1" t="inlineStr">
         <is>
           <t>PROFIT DATE 48</t>
         </is>
       </c>
-      <c r="EV1" t="inlineStr">
+      <c r="FI1" t="inlineStr">
         <is>
           <t>PAID_48</t>
         </is>
       </c>
-      <c r="EW1" t="inlineStr">
+      <c r="FJ1" t="inlineStr">
         <is>
           <t>PAYMENT_DATE_48</t>
         </is>
       </c>
-      <c r="EX1" t="inlineStr">
+      <c r="FK1" t="inlineStr">
         <is>
           <t>PROFIT DATE 49</t>
         </is>
       </c>
-      <c r="EY1" t="inlineStr">
+      <c r="FL1" t="inlineStr">
         <is>
           <t>PAID_49</t>
         </is>
       </c>
-      <c r="EZ1" t="inlineStr">
+      <c r="FM1" t="inlineStr">
         <is>
           <t>PAYMENT_DATE_49</t>
         </is>
       </c>
-      <c r="FA1" t="inlineStr">
+      <c r="FN1" t="inlineStr">
         <is>
           <t>PROFIT DATE 50</t>
         </is>
       </c>
-      <c r="FB1" t="inlineStr">
+      <c r="FO1" t="inlineStr">
         <is>
           <t>PAID_50</t>
         </is>
       </c>
-      <c r="FC1" t="inlineStr">
+      <c r="FP1" t="inlineStr">
         <is>
           <t>PAYMENT_DATE_50</t>
         </is>
       </c>
-      <c r="FD1" t="inlineStr">
+      <c r="FQ1" t="inlineStr">
         <is>
           <t>PROFIT DATE 51</t>
         </is>
       </c>
-      <c r="FE1" t="inlineStr">
+      <c r="FR1" t="inlineStr">
         <is>
           <t>PAID_51</t>
         </is>
       </c>
-      <c r="FF1" t="inlineStr">
+      <c r="FS1" t="inlineStr">
         <is>
           <t>PAYMENT_DATE_51</t>
         </is>
       </c>
-      <c r="FG1" t="inlineStr">
+      <c r="FT1" t="inlineStr">
         <is>
           <t>PROFIT DATE 52</t>
         </is>
       </c>
-      <c r="FH1" t="inlineStr">
+      <c r="FU1" t="inlineStr">
         <is>
           <t>PAID_52</t>
         </is>
       </c>
-      <c r="FI1" t="inlineStr">
+      <c r="FV1" t="inlineStr">
         <is>
           <t>PAYMENT_DATE_52</t>
         </is>
       </c>
-      <c r="FJ1" t="inlineStr">
+      <c r="FW1" t="inlineStr">
         <is>
           <t>PROFIT DATE 53</t>
         </is>
       </c>
-      <c r="FK1" t="inlineStr">
+      <c r="FX1" t="inlineStr">
         <is>
           <t>PAID_53</t>
         </is>
       </c>
-      <c r="FL1" t="inlineStr">
+      <c r="FY1" t="inlineStr">
         <is>
           <t>PAYMENT_DATE_53</t>
         </is>
       </c>
-      <c r="FM1" t="inlineStr">
+      <c r="FZ1" t="inlineStr">
         <is>
           <t>PROFIT DATE 54</t>
         </is>
       </c>
-      <c r="FN1" t="inlineStr">
+      <c r="GA1" t="inlineStr">
         <is>
           <t>PAID_54</t>
         </is>
       </c>
-      <c r="FO1" t="inlineStr">
+      <c r="GB1" t="inlineStr">
         <is>
           <t>PAYMENT_DATE_54</t>
         </is>
       </c>
-      <c r="FP1" t="inlineStr">
+      <c r="GC1" t="inlineStr">
         <is>
           <t>PROFIT DATE 55</t>
         </is>
       </c>
-      <c r="FQ1" t="inlineStr">
+      <c r="GD1" t="inlineStr">
         <is>
           <t>PAID_55</t>
         </is>
       </c>
-      <c r="FR1" t="inlineStr">
+      <c r="GE1" t="inlineStr">
         <is>
           <t>PAYMENT_DATE_55</t>
         </is>
       </c>
-      <c r="FS1" t="inlineStr">
+      <c r="GF1" t="inlineStr">
         <is>
           <t>PROFIT DATE 56</t>
         </is>
       </c>
-      <c r="FT1" t="inlineStr">
+      <c r="GG1" t="inlineStr">
         <is>
           <t>PAID_56</t>
         </is>
       </c>
-      <c r="FU1" t="inlineStr">
+      <c r="GH1" t="inlineStr">
         <is>
           <t>PAYMENT_DATE_56</t>
         </is>
       </c>
-      <c r="FV1" t="inlineStr">
+      <c r="GI1" t="inlineStr">
         <is>
           <t>PROFIT DATE 57</t>
         </is>
       </c>
-      <c r="FW1" t="inlineStr">
+      <c r="GJ1" t="inlineStr">
         <is>
           <t>PAID_57</t>
         </is>
       </c>
-      <c r="FX1" t="inlineStr">
+      <c r="GK1" t="inlineStr">
         <is>
           <t>PAYMENT_DATE_57</t>
         </is>
       </c>
-      <c r="FY1" t="inlineStr">
+      <c r="GL1" t="inlineStr">
         <is>
           <t>PROFIT DATE 58</t>
         </is>
       </c>
-      <c r="FZ1" t="inlineStr">
+      <c r="GM1" t="inlineStr">
         <is>
           <t>PAID_58</t>
         </is>
       </c>
-      <c r="GA1" t="inlineStr">
+      <c r="GN1" t="inlineStr">
         <is>
           <t>PAYMENT_DATE_58</t>
         </is>
       </c>
-      <c r="GB1" t="inlineStr">
+      <c r="GO1" t="inlineStr">
         <is>
           <t>PROFIT DATE 59</t>
         </is>
       </c>
-      <c r="GC1" t="inlineStr">
+      <c r="GP1" t="inlineStr">
         <is>
           <t>PAID_59</t>
         </is>
       </c>
-      <c r="GD1" t="inlineStr">
+      <c r="GQ1" t="inlineStr">
         <is>
           <t>PAYMENT_DATE_59</t>
         </is>
       </c>
-      <c r="GE1" t="inlineStr">
+      <c r="GR1" t="inlineStr">
         <is>
           <t>PROFIT DATE 60</t>
         </is>
       </c>
-      <c r="GF1" t="inlineStr">
+      <c r="GS1" t="inlineStr">
         <is>
           <t>PAID_60</t>
         </is>
       </c>
-      <c r="GG1" t="inlineStr">
+      <c r="GT1" t="inlineStr">
         <is>
           <t>PAYMENT_DATE_60</t>
         </is>
@@ -1370,716 +1438,802 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>Satish Patole</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>9832641274</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="n">
+        <v>46023</v>
+      </c>
+      <c r="D2" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>FLPP</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="H2" t="n">
+        <v>100</v>
+      </c>
+      <c r="I2" s="1" t="n">
+        <v>46446</v>
+      </c>
+      <c r="J2" t="b">
+        <v>0</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
           <t>Harshala Patole</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>987457352</v>
-      </c>
-      <c r="C2" s="1" t="n">
+      <c r="L2" t="n">
+        <v>100000</v>
+      </c>
+      <c r="M2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+      <c r="O2" t="n">
+        <v>10</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>ICICI Bank</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Satish Patole</t>
+        </is>
+      </c>
+      <c r="R2" t="n">
+        <v>23648729978421</v>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>ICIC00000564</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>Mahape</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>uyuweyruiywer</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>asfasfsf</t>
+        </is>
+      </c>
+      <c r="W2" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="X2" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="AA2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" s="1" t="n">
         <v>46113</v>
       </c>
-      <c r="D2" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>jmd 6.0</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>6</v>
-      </c>
-      <c r="G2" t="n">
-        <v>500000</v>
-      </c>
-      <c r="H2" s="1" t="n">
-        <v>46387</v>
-      </c>
-      <c r="I2" t="b">
-        <v>0</v>
-      </c>
-      <c r="J2" s="1" t="n">
+      <c r="AD2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" s="1" t="n">
         <v>46143</v>
       </c>
-      <c r="K2" t="b">
-        <v>1</v>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>30-05-2026 08:45:13</t>
-        </is>
-      </c>
-      <c r="M2" s="1" t="n">
+      <c r="AG2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" s="1" t="n">
         <v>46174</v>
       </c>
-      <c r="N2" t="b">
-        <v>0</v>
-      </c>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" s="1" t="n">
+      <c r="AJ2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" s="1" t="n">
         <v>46204</v>
       </c>
-      <c r="Q2" t="b">
-        <v>0</v>
-      </c>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" s="1" t="n">
+      <c r="AM2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" s="1" t="n">
         <v>46235</v>
       </c>
-      <c r="T2" t="b">
-        <v>0</v>
-      </c>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" s="1" t="n">
+      <c r="AP2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" s="1" t="n">
         <v>46266</v>
       </c>
-      <c r="W2" t="b">
-        <v>0</v>
-      </c>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" s="1" t="n">
+      <c r="AS2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" s="1" t="n">
         <v>46296</v>
       </c>
-      <c r="Z2" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA2" t="inlineStr"/>
-      <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD2" t="inlineStr"/>
-      <c r="AE2" t="inlineStr"/>
-      <c r="AF2" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG2" t="inlineStr"/>
-      <c r="AH2" t="inlineStr"/>
-      <c r="AI2" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ2" t="inlineStr"/>
-      <c r="AK2" t="inlineStr"/>
-      <c r="AL2" t="b">
-        <v>0</v>
-      </c>
-      <c r="AM2" t="inlineStr"/>
-      <c r="AN2" t="inlineStr"/>
-      <c r="AO2" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP2" t="inlineStr"/>
-      <c r="AQ2" t="inlineStr"/>
-      <c r="AR2" t="b">
-        <v>0</v>
-      </c>
-      <c r="AS2" t="inlineStr"/>
-      <c r="AT2" t="inlineStr"/>
-      <c r="AU2" t="b">
-        <v>0</v>
-      </c>
-      <c r="AV2" t="inlineStr"/>
+      <c r="AV2" t="b">
+        <v>0</v>
+      </c>
       <c r="AW2" t="inlineStr"/>
-      <c r="AX2" t="b">
-        <v>0</v>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AX2" s="1" t="n">
+        <v>46327</v>
+      </c>
+      <c r="AY2" t="b">
+        <v>0</v>
+      </c>
       <c r="AZ2" t="inlineStr"/>
-      <c r="BA2" t="b">
-        <v>0</v>
-      </c>
-      <c r="BB2" t="inlineStr"/>
+      <c r="BA2" t="inlineStr"/>
+      <c r="BB2" t="b">
+        <v>0</v>
+      </c>
       <c r="BC2" t="inlineStr"/>
-      <c r="BD2" t="b">
-        <v>0</v>
-      </c>
-      <c r="BE2" t="inlineStr"/>
+      <c r="BD2" t="inlineStr"/>
+      <c r="BE2" t="b">
+        <v>0</v>
+      </c>
       <c r="BF2" t="inlineStr"/>
-      <c r="BG2" t="b">
-        <v>0</v>
-      </c>
-      <c r="BH2" t="inlineStr"/>
+      <c r="BG2" t="inlineStr"/>
+      <c r="BH2" t="b">
+        <v>0</v>
+      </c>
       <c r="BI2" t="inlineStr"/>
-      <c r="BJ2" t="b">
-        <v>0</v>
-      </c>
-      <c r="BK2" t="inlineStr"/>
+      <c r="BJ2" t="inlineStr"/>
+      <c r="BK2" t="b">
+        <v>0</v>
+      </c>
       <c r="BL2" t="inlineStr"/>
-      <c r="BM2" t="b">
-        <v>0</v>
-      </c>
-      <c r="BN2" t="inlineStr"/>
+      <c r="BM2" t="inlineStr"/>
+      <c r="BN2" t="b">
+        <v>0</v>
+      </c>
       <c r="BO2" t="inlineStr"/>
-      <c r="BP2" t="b">
-        <v>0</v>
-      </c>
-      <c r="BQ2" t="inlineStr"/>
+      <c r="BP2" t="inlineStr"/>
+      <c r="BQ2" t="b">
+        <v>0</v>
+      </c>
       <c r="BR2" t="inlineStr"/>
-      <c r="BS2" t="b">
-        <v>0</v>
-      </c>
-      <c r="BT2" t="inlineStr"/>
+      <c r="BS2" t="inlineStr"/>
+      <c r="BT2" t="b">
+        <v>0</v>
+      </c>
       <c r="BU2" t="inlineStr"/>
-      <c r="BV2" t="b">
-        <v>0</v>
-      </c>
-      <c r="BW2" t="inlineStr"/>
+      <c r="BV2" t="inlineStr"/>
+      <c r="BW2" t="b">
+        <v>0</v>
+      </c>
       <c r="BX2" t="inlineStr"/>
-      <c r="BY2" t="b">
-        <v>0</v>
-      </c>
-      <c r="BZ2" t="inlineStr"/>
+      <c r="BY2" t="inlineStr"/>
+      <c r="BZ2" t="b">
+        <v>0</v>
+      </c>
       <c r="CA2" t="inlineStr"/>
-      <c r="CB2" t="b">
-        <v>0</v>
-      </c>
-      <c r="CC2" t="inlineStr"/>
+      <c r="CB2" t="inlineStr"/>
+      <c r="CC2" t="b">
+        <v>0</v>
+      </c>
       <c r="CD2" t="inlineStr"/>
-      <c r="CE2" t="b">
-        <v>0</v>
-      </c>
-      <c r="CF2" t="inlineStr"/>
+      <c r="CE2" t="inlineStr"/>
+      <c r="CF2" t="b">
+        <v>0</v>
+      </c>
       <c r="CG2" t="inlineStr"/>
-      <c r="CH2" t="b">
-        <v>0</v>
-      </c>
-      <c r="CI2" t="inlineStr"/>
+      <c r="CH2" t="inlineStr"/>
+      <c r="CI2" t="b">
+        <v>0</v>
+      </c>
       <c r="CJ2" t="inlineStr"/>
-      <c r="CK2" t="b">
-        <v>0</v>
-      </c>
-      <c r="CL2" t="inlineStr"/>
+      <c r="CK2" t="inlineStr"/>
+      <c r="CL2" t="b">
+        <v>0</v>
+      </c>
       <c r="CM2" t="inlineStr"/>
-      <c r="CN2" t="b">
-        <v>0</v>
-      </c>
-      <c r="CO2" t="inlineStr"/>
+      <c r="CN2" t="inlineStr"/>
+      <c r="CO2" t="b">
+        <v>0</v>
+      </c>
       <c r="CP2" t="inlineStr"/>
-      <c r="CQ2" t="b">
-        <v>0</v>
-      </c>
-      <c r="CR2" t="inlineStr"/>
+      <c r="CQ2" t="inlineStr"/>
+      <c r="CR2" t="b">
+        <v>0</v>
+      </c>
       <c r="CS2" t="inlineStr"/>
-      <c r="CT2" t="b">
-        <v>0</v>
-      </c>
-      <c r="CU2" t="inlineStr"/>
+      <c r="CT2" t="inlineStr"/>
+      <c r="CU2" t="b">
+        <v>0</v>
+      </c>
       <c r="CV2" t="inlineStr"/>
-      <c r="CW2" t="b">
-        <v>0</v>
-      </c>
-      <c r="CX2" t="inlineStr"/>
+      <c r="CW2" t="inlineStr"/>
+      <c r="CX2" t="b">
+        <v>0</v>
+      </c>
       <c r="CY2" t="inlineStr"/>
-      <c r="CZ2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DA2" t="inlineStr"/>
+      <c r="CZ2" t="inlineStr"/>
+      <c r="DA2" t="b">
+        <v>0</v>
+      </c>
       <c r="DB2" t="inlineStr"/>
-      <c r="DC2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DD2" t="inlineStr"/>
+      <c r="DC2" t="inlineStr"/>
+      <c r="DD2" t="b">
+        <v>0</v>
+      </c>
       <c r="DE2" t="inlineStr"/>
-      <c r="DF2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DG2" t="inlineStr"/>
+      <c r="DF2" t="inlineStr"/>
+      <c r="DG2" t="b">
+        <v>0</v>
+      </c>
       <c r="DH2" t="inlineStr"/>
-      <c r="DI2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DJ2" t="inlineStr"/>
+      <c r="DI2" t="inlineStr"/>
+      <c r="DJ2" t="b">
+        <v>0</v>
+      </c>
       <c r="DK2" t="inlineStr"/>
-      <c r="DL2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DM2" t="inlineStr"/>
+      <c r="DL2" t="inlineStr"/>
+      <c r="DM2" t="b">
+        <v>0</v>
+      </c>
       <c r="DN2" t="inlineStr"/>
-      <c r="DO2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DP2" t="inlineStr"/>
+      <c r="DO2" t="inlineStr"/>
+      <c r="DP2" t="b">
+        <v>0</v>
+      </c>
       <c r="DQ2" t="inlineStr"/>
-      <c r="DR2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DS2" t="inlineStr"/>
+      <c r="DR2" t="inlineStr"/>
+      <c r="DS2" t="b">
+        <v>0</v>
+      </c>
       <c r="DT2" t="inlineStr"/>
-      <c r="DU2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DV2" t="inlineStr"/>
+      <c r="DU2" t="inlineStr"/>
+      <c r="DV2" t="b">
+        <v>0</v>
+      </c>
       <c r="DW2" t="inlineStr"/>
-      <c r="DX2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DY2" t="inlineStr"/>
+      <c r="DX2" t="inlineStr"/>
+      <c r="DY2" t="b">
+        <v>0</v>
+      </c>
       <c r="DZ2" t="inlineStr"/>
-      <c r="EA2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EB2" t="inlineStr"/>
+      <c r="EA2" t="inlineStr"/>
+      <c r="EB2" t="b">
+        <v>0</v>
+      </c>
       <c r="EC2" t="inlineStr"/>
-      <c r="ED2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EE2" t="inlineStr"/>
+      <c r="ED2" t="inlineStr"/>
+      <c r="EE2" t="b">
+        <v>0</v>
+      </c>
       <c r="EF2" t="inlineStr"/>
-      <c r="EG2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EH2" t="inlineStr"/>
+      <c r="EG2" t="inlineStr"/>
+      <c r="EH2" t="b">
+        <v>0</v>
+      </c>
       <c r="EI2" t="inlineStr"/>
-      <c r="EJ2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EK2" t="inlineStr"/>
+      <c r="EJ2" t="inlineStr"/>
+      <c r="EK2" t="b">
+        <v>0</v>
+      </c>
       <c r="EL2" t="inlineStr"/>
-      <c r="EM2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EN2" t="inlineStr"/>
+      <c r="EM2" t="inlineStr"/>
+      <c r="EN2" t="b">
+        <v>0</v>
+      </c>
       <c r="EO2" t="inlineStr"/>
-      <c r="EP2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EQ2" t="inlineStr"/>
+      <c r="EP2" t="inlineStr"/>
+      <c r="EQ2" t="b">
+        <v>0</v>
+      </c>
       <c r="ER2" t="inlineStr"/>
-      <c r="ES2" t="b">
-        <v>0</v>
-      </c>
-      <c r="ET2" t="inlineStr"/>
+      <c r="ES2" t="inlineStr"/>
+      <c r="ET2" t="b">
+        <v>0</v>
+      </c>
       <c r="EU2" t="inlineStr"/>
-      <c r="EV2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EW2" t="inlineStr"/>
+      <c r="EV2" t="inlineStr"/>
+      <c r="EW2" t="b">
+        <v>0</v>
+      </c>
       <c r="EX2" t="inlineStr"/>
-      <c r="EY2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EZ2" t="inlineStr"/>
+      <c r="EY2" t="inlineStr"/>
+      <c r="EZ2" t="b">
+        <v>0</v>
+      </c>
       <c r="FA2" t="inlineStr"/>
-      <c r="FB2" t="b">
-        <v>0</v>
-      </c>
-      <c r="FC2" t="inlineStr"/>
+      <c r="FB2" t="inlineStr"/>
+      <c r="FC2" t="b">
+        <v>0</v>
+      </c>
       <c r="FD2" t="inlineStr"/>
-      <c r="FE2" t="b">
-        <v>0</v>
-      </c>
-      <c r="FF2" t="inlineStr"/>
+      <c r="FE2" t="inlineStr"/>
+      <c r="FF2" t="b">
+        <v>0</v>
+      </c>
       <c r="FG2" t="inlineStr"/>
-      <c r="FH2" t="b">
-        <v>0</v>
-      </c>
-      <c r="FI2" t="inlineStr"/>
+      <c r="FH2" t="inlineStr"/>
+      <c r="FI2" t="b">
+        <v>0</v>
+      </c>
       <c r="FJ2" t="inlineStr"/>
-      <c r="FK2" t="b">
-        <v>0</v>
-      </c>
-      <c r="FL2" t="inlineStr"/>
+      <c r="FK2" t="inlineStr"/>
+      <c r="FL2" t="b">
+        <v>0</v>
+      </c>
       <c r="FM2" t="inlineStr"/>
-      <c r="FN2" t="b">
-        <v>0</v>
-      </c>
-      <c r="FO2" t="inlineStr"/>
+      <c r="FN2" t="inlineStr"/>
+      <c r="FO2" t="b">
+        <v>0</v>
+      </c>
       <c r="FP2" t="inlineStr"/>
-      <c r="FQ2" t="b">
-        <v>0</v>
-      </c>
-      <c r="FR2" t="inlineStr"/>
+      <c r="FQ2" t="inlineStr"/>
+      <c r="FR2" t="b">
+        <v>0</v>
+      </c>
       <c r="FS2" t="inlineStr"/>
-      <c r="FT2" t="b">
-        <v>0</v>
-      </c>
-      <c r="FU2" t="inlineStr"/>
+      <c r="FT2" t="inlineStr"/>
+      <c r="FU2" t="b">
+        <v>0</v>
+      </c>
       <c r="FV2" t="inlineStr"/>
-      <c r="FW2" t="b">
-        <v>0</v>
-      </c>
-      <c r="FX2" t="inlineStr"/>
+      <c r="FW2" t="inlineStr"/>
+      <c r="FX2" t="b">
+        <v>0</v>
+      </c>
       <c r="FY2" t="inlineStr"/>
-      <c r="FZ2" t="b">
-        <v>0</v>
-      </c>
-      <c r="GA2" t="inlineStr"/>
+      <c r="FZ2" t="inlineStr"/>
+      <c r="GA2" t="b">
+        <v>0</v>
+      </c>
       <c r="GB2" t="inlineStr"/>
-      <c r="GC2" t="b">
-        <v>0</v>
-      </c>
-      <c r="GD2" t="inlineStr"/>
+      <c r="GC2" t="inlineStr"/>
+      <c r="GD2" t="b">
+        <v>0</v>
+      </c>
       <c r="GE2" t="inlineStr"/>
-      <c r="GF2" t="b">
-        <v>0</v>
-      </c>
-      <c r="GG2" t="inlineStr"/>
+      <c r="GF2" t="inlineStr"/>
+      <c r="GG2" t="b">
+        <v>0</v>
+      </c>
+      <c r="GH2" t="inlineStr"/>
+      <c r="GI2" t="inlineStr"/>
+      <c r="GJ2" t="b">
+        <v>0</v>
+      </c>
+      <c r="GK2" t="inlineStr"/>
+      <c r="GL2" t="inlineStr"/>
+      <c r="GM2" t="b">
+        <v>0</v>
+      </c>
+      <c r="GN2" t="inlineStr"/>
+      <c r="GO2" t="inlineStr"/>
+      <c r="GP2" t="b">
+        <v>0</v>
+      </c>
+      <c r="GQ2" t="inlineStr"/>
+      <c r="GR2" t="inlineStr"/>
+      <c r="GS2" t="b">
+        <v>0</v>
+      </c>
+      <c r="GT2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Ajay Bhosale</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>9874623097</v>
+          <t>Nikhil Bhosle</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>9847575374</t>
+        </is>
       </c>
       <c r="C3" s="1" t="n">
-        <v>46082</v>
+        <v>46143</v>
       </c>
       <c r="D3" t="n">
         <v>5000000</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>jmd 6.0</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>12</v>
-      </c>
+          <t>JMD1.0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="n">
         <v>2500000</v>
       </c>
-      <c r="H3" s="1" t="n">
-        <v>46508</v>
-      </c>
-      <c r="I3" t="b">
-        <v>0</v>
-      </c>
-      <c r="J3" s="1" t="n">
-        <v>46113</v>
-      </c>
-      <c r="K3" t="b">
-        <v>1</v>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>30-05-2026 08:45:51</t>
-        </is>
-      </c>
-      <c r="M3" s="1" t="n">
-        <v>46143</v>
-      </c>
-      <c r="N3" t="b">
-        <v>1</v>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>30-05-2026 08:48:00</t>
-        </is>
-      </c>
-      <c r="P3" s="1" t="n">
-        <v>46174</v>
-      </c>
-      <c r="Q3" t="b">
-        <v>0</v>
-      </c>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" s="1" t="n">
-        <v>46204</v>
-      </c>
-      <c r="T3" t="b">
-        <v>0</v>
-      </c>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" s="1" t="n">
-        <v>46235</v>
-      </c>
-      <c r="W3" t="b">
-        <v>0</v>
-      </c>
-      <c r="X3" t="inlineStr"/>
-      <c r="Y3" s="1" t="n">
-        <v>46235</v>
-      </c>
-      <c r="Z3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA3" t="inlineStr"/>
-      <c r="AB3" s="1" t="n">
-        <v>46266</v>
-      </c>
-      <c r="AC3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD3" t="inlineStr"/>
-      <c r="AE3" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="AF3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="inlineStr"/>
-      <c r="AH3" s="1" t="n">
-        <v>46327</v>
-      </c>
-      <c r="AI3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ3" t="inlineStr"/>
-      <c r="AK3" s="1" t="n">
-        <v>46357</v>
-      </c>
-      <c r="AL3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AM3" t="inlineStr"/>
-      <c r="AN3" s="1" t="n">
-        <v>46388</v>
-      </c>
-      <c r="AO3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP3" t="inlineStr"/>
-      <c r="AQ3" s="1" t="n">
-        <v>46419</v>
-      </c>
-      <c r="AR3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AS3" t="inlineStr"/>
+      <c r="H3" t="n">
+        <v>50</v>
+      </c>
+      <c r="I3" s="1" t="n">
+        <v>46172</v>
+      </c>
+      <c r="J3" t="b">
+        <v>0</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Mandar Dhumal</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>450000</v>
+      </c>
+      <c r="M3" t="b">
+        <v>0</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Yearly</t>
+        </is>
+      </c>
+      <c r="O3" t="n">
+        <v>2</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>HDFC BANK</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>Nikhil Bhosle</t>
+        </is>
+      </c>
+      <c r="R3" t="n">
+        <v>7868273643223</v>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>HDFC000764</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Dadar</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>BNVDSNBFVDSH</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>AMNDB678A77A</t>
+        </is>
+      </c>
+      <c r="W3" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="X3" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" s="1" t="n">
+        <v>46903</v>
+      </c>
+      <c r="AA3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="inlineStr"/>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr"/>
+      <c r="AI3" t="inlineStr"/>
+      <c r="AJ3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK3" t="inlineStr"/>
+      <c r="AL3" t="inlineStr"/>
+      <c r="AM3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AN3" t="inlineStr"/>
+      <c r="AO3" t="inlineStr"/>
+      <c r="AP3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AQ3" t="inlineStr"/>
+      <c r="AR3" t="inlineStr"/>
+      <c r="AS3" t="b">
+        <v>0</v>
+      </c>
       <c r="AT3" t="inlineStr"/>
-      <c r="AU3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AV3" t="inlineStr"/>
+      <c r="AU3" t="inlineStr"/>
+      <c r="AV3" t="b">
+        <v>0</v>
+      </c>
       <c r="AW3" t="inlineStr"/>
-      <c r="AX3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AX3" t="inlineStr"/>
+      <c r="AY3" t="b">
+        <v>0</v>
+      </c>
       <c r="AZ3" t="inlineStr"/>
-      <c r="BA3" t="b">
-        <v>0</v>
-      </c>
-      <c r="BB3" t="inlineStr"/>
+      <c r="BA3" t="inlineStr"/>
+      <c r="BB3" t="b">
+        <v>0</v>
+      </c>
       <c r="BC3" t="inlineStr"/>
-      <c r="BD3" t="b">
-        <v>0</v>
-      </c>
-      <c r="BE3" t="inlineStr"/>
+      <c r="BD3" t="inlineStr"/>
+      <c r="BE3" t="b">
+        <v>0</v>
+      </c>
       <c r="BF3" t="inlineStr"/>
-      <c r="BG3" t="b">
-        <v>0</v>
-      </c>
-      <c r="BH3" t="inlineStr"/>
+      <c r="BG3" t="inlineStr"/>
+      <c r="BH3" t="b">
+        <v>0</v>
+      </c>
       <c r="BI3" t="inlineStr"/>
-      <c r="BJ3" t="b">
-        <v>0</v>
-      </c>
-      <c r="BK3" t="inlineStr"/>
+      <c r="BJ3" t="inlineStr"/>
+      <c r="BK3" t="b">
+        <v>0</v>
+      </c>
       <c r="BL3" t="inlineStr"/>
-      <c r="BM3" t="b">
-        <v>0</v>
-      </c>
-      <c r="BN3" t="inlineStr"/>
+      <c r="BM3" t="inlineStr"/>
+      <c r="BN3" t="b">
+        <v>0</v>
+      </c>
       <c r="BO3" t="inlineStr"/>
-      <c r="BP3" t="b">
-        <v>0</v>
-      </c>
-      <c r="BQ3" t="inlineStr"/>
+      <c r="BP3" t="inlineStr"/>
+      <c r="BQ3" t="b">
+        <v>0</v>
+      </c>
       <c r="BR3" t="inlineStr"/>
-      <c r="BS3" t="b">
-        <v>0</v>
-      </c>
-      <c r="BT3" t="inlineStr"/>
+      <c r="BS3" t="inlineStr"/>
+      <c r="BT3" t="b">
+        <v>0</v>
+      </c>
       <c r="BU3" t="inlineStr"/>
-      <c r="BV3" t="b">
-        <v>0</v>
-      </c>
-      <c r="BW3" t="inlineStr"/>
+      <c r="BV3" t="inlineStr"/>
+      <c r="BW3" t="b">
+        <v>0</v>
+      </c>
       <c r="BX3" t="inlineStr"/>
-      <c r="BY3" t="b">
-        <v>0</v>
-      </c>
-      <c r="BZ3" t="inlineStr"/>
+      <c r="BY3" t="inlineStr"/>
+      <c r="BZ3" t="b">
+        <v>0</v>
+      </c>
       <c r="CA3" t="inlineStr"/>
-      <c r="CB3" t="b">
-        <v>0</v>
-      </c>
-      <c r="CC3" t="inlineStr"/>
+      <c r="CB3" t="inlineStr"/>
+      <c r="CC3" t="b">
+        <v>0</v>
+      </c>
       <c r="CD3" t="inlineStr"/>
-      <c r="CE3" t="b">
-        <v>0</v>
-      </c>
-      <c r="CF3" t="inlineStr"/>
+      <c r="CE3" t="inlineStr"/>
+      <c r="CF3" t="b">
+        <v>0</v>
+      </c>
       <c r="CG3" t="inlineStr"/>
-      <c r="CH3" t="b">
-        <v>0</v>
-      </c>
-      <c r="CI3" t="inlineStr"/>
+      <c r="CH3" t="inlineStr"/>
+      <c r="CI3" t="b">
+        <v>0</v>
+      </c>
       <c r="CJ3" t="inlineStr"/>
-      <c r="CK3" t="b">
-        <v>0</v>
-      </c>
-      <c r="CL3" t="inlineStr"/>
+      <c r="CK3" t="inlineStr"/>
+      <c r="CL3" t="b">
+        <v>0</v>
+      </c>
       <c r="CM3" t="inlineStr"/>
-      <c r="CN3" t="b">
-        <v>0</v>
-      </c>
-      <c r="CO3" t="inlineStr"/>
+      <c r="CN3" t="inlineStr"/>
+      <c r="CO3" t="b">
+        <v>0</v>
+      </c>
       <c r="CP3" t="inlineStr"/>
-      <c r="CQ3" t="b">
-        <v>0</v>
-      </c>
-      <c r="CR3" t="inlineStr"/>
+      <c r="CQ3" t="inlineStr"/>
+      <c r="CR3" t="b">
+        <v>0</v>
+      </c>
       <c r="CS3" t="inlineStr"/>
-      <c r="CT3" t="b">
-        <v>0</v>
-      </c>
-      <c r="CU3" t="inlineStr"/>
+      <c r="CT3" t="inlineStr"/>
+      <c r="CU3" t="b">
+        <v>0</v>
+      </c>
       <c r="CV3" t="inlineStr"/>
-      <c r="CW3" t="b">
-        <v>0</v>
-      </c>
-      <c r="CX3" t="inlineStr"/>
+      <c r="CW3" t="inlineStr"/>
+      <c r="CX3" t="b">
+        <v>0</v>
+      </c>
       <c r="CY3" t="inlineStr"/>
-      <c r="CZ3" t="b">
-        <v>0</v>
-      </c>
-      <c r="DA3" t="inlineStr"/>
+      <c r="CZ3" t="inlineStr"/>
+      <c r="DA3" t="b">
+        <v>0</v>
+      </c>
       <c r="DB3" t="inlineStr"/>
-      <c r="DC3" t="b">
-        <v>0</v>
-      </c>
-      <c r="DD3" t="inlineStr"/>
+      <c r="DC3" t="inlineStr"/>
+      <c r="DD3" t="b">
+        <v>0</v>
+      </c>
       <c r="DE3" t="inlineStr"/>
-      <c r="DF3" t="b">
-        <v>0</v>
-      </c>
-      <c r="DG3" t="inlineStr"/>
+      <c r="DF3" t="inlineStr"/>
+      <c r="DG3" t="b">
+        <v>0</v>
+      </c>
       <c r="DH3" t="inlineStr"/>
-      <c r="DI3" t="b">
-        <v>0</v>
-      </c>
-      <c r="DJ3" t="inlineStr"/>
+      <c r="DI3" t="inlineStr"/>
+      <c r="DJ3" t="b">
+        <v>0</v>
+      </c>
       <c r="DK3" t="inlineStr"/>
-      <c r="DL3" t="b">
-        <v>0</v>
-      </c>
-      <c r="DM3" t="inlineStr"/>
+      <c r="DL3" t="inlineStr"/>
+      <c r="DM3" t="b">
+        <v>0</v>
+      </c>
       <c r="DN3" t="inlineStr"/>
-      <c r="DO3" t="b">
-        <v>0</v>
-      </c>
-      <c r="DP3" t="inlineStr"/>
+      <c r="DO3" t="inlineStr"/>
+      <c r="DP3" t="b">
+        <v>0</v>
+      </c>
       <c r="DQ3" t="inlineStr"/>
-      <c r="DR3" t="b">
-        <v>0</v>
-      </c>
-      <c r="DS3" t="inlineStr"/>
+      <c r="DR3" t="inlineStr"/>
+      <c r="DS3" t="b">
+        <v>0</v>
+      </c>
       <c r="DT3" t="inlineStr"/>
-      <c r="DU3" t="b">
-        <v>0</v>
-      </c>
-      <c r="DV3" t="inlineStr"/>
+      <c r="DU3" t="inlineStr"/>
+      <c r="DV3" t="b">
+        <v>0</v>
+      </c>
       <c r="DW3" t="inlineStr"/>
-      <c r="DX3" t="b">
-        <v>0</v>
-      </c>
-      <c r="DY3" t="inlineStr"/>
+      <c r="DX3" t="inlineStr"/>
+      <c r="DY3" t="b">
+        <v>0</v>
+      </c>
       <c r="DZ3" t="inlineStr"/>
-      <c r="EA3" t="b">
-        <v>0</v>
-      </c>
-      <c r="EB3" t="inlineStr"/>
+      <c r="EA3" t="inlineStr"/>
+      <c r="EB3" t="b">
+        <v>0</v>
+      </c>
       <c r="EC3" t="inlineStr"/>
-      <c r="ED3" t="b">
-        <v>0</v>
-      </c>
-      <c r="EE3" t="inlineStr"/>
+      <c r="ED3" t="inlineStr"/>
+      <c r="EE3" t="b">
+        <v>0</v>
+      </c>
       <c r="EF3" t="inlineStr"/>
-      <c r="EG3" t="b">
-        <v>0</v>
-      </c>
-      <c r="EH3" t="inlineStr"/>
+      <c r="EG3" t="inlineStr"/>
+      <c r="EH3" t="b">
+        <v>0</v>
+      </c>
       <c r="EI3" t="inlineStr"/>
-      <c r="EJ3" t="b">
-        <v>0</v>
-      </c>
-      <c r="EK3" t="inlineStr"/>
+      <c r="EJ3" t="inlineStr"/>
+      <c r="EK3" t="b">
+        <v>0</v>
+      </c>
       <c r="EL3" t="inlineStr"/>
-      <c r="EM3" t="b">
-        <v>0</v>
-      </c>
-      <c r="EN3" t="inlineStr"/>
+      <c r="EM3" t="inlineStr"/>
+      <c r="EN3" t="b">
+        <v>0</v>
+      </c>
       <c r="EO3" t="inlineStr"/>
-      <c r="EP3" t="b">
-        <v>0</v>
-      </c>
-      <c r="EQ3" t="inlineStr"/>
+      <c r="EP3" t="inlineStr"/>
+      <c r="EQ3" t="b">
+        <v>0</v>
+      </c>
       <c r="ER3" t="inlineStr"/>
-      <c r="ES3" t="b">
-        <v>0</v>
-      </c>
-      <c r="ET3" t="inlineStr"/>
+      <c r="ES3" t="inlineStr"/>
+      <c r="ET3" t="b">
+        <v>0</v>
+      </c>
       <c r="EU3" t="inlineStr"/>
-      <c r="EV3" t="b">
-        <v>0</v>
-      </c>
-      <c r="EW3" t="inlineStr"/>
+      <c r="EV3" t="inlineStr"/>
+      <c r="EW3" t="b">
+        <v>0</v>
+      </c>
       <c r="EX3" t="inlineStr"/>
-      <c r="EY3" t="b">
-        <v>0</v>
-      </c>
-      <c r="EZ3" t="inlineStr"/>
+      <c r="EY3" t="inlineStr"/>
+      <c r="EZ3" t="b">
+        <v>0</v>
+      </c>
       <c r="FA3" t="inlineStr"/>
-      <c r="FB3" t="b">
-        <v>0</v>
-      </c>
-      <c r="FC3" t="inlineStr"/>
+      <c r="FB3" t="inlineStr"/>
+      <c r="FC3" t="b">
+        <v>0</v>
+      </c>
       <c r="FD3" t="inlineStr"/>
-      <c r="FE3" t="b">
-        <v>0</v>
-      </c>
-      <c r="FF3" t="inlineStr"/>
+      <c r="FE3" t="inlineStr"/>
+      <c r="FF3" t="b">
+        <v>0</v>
+      </c>
       <c r="FG3" t="inlineStr"/>
-      <c r="FH3" t="b">
-        <v>0</v>
-      </c>
-      <c r="FI3" t="inlineStr"/>
+      <c r="FH3" t="inlineStr"/>
+      <c r="FI3" t="b">
+        <v>0</v>
+      </c>
       <c r="FJ3" t="inlineStr"/>
-      <c r="FK3" t="b">
-        <v>0</v>
-      </c>
-      <c r="FL3" t="inlineStr"/>
+      <c r="FK3" t="inlineStr"/>
+      <c r="FL3" t="b">
+        <v>0</v>
+      </c>
       <c r="FM3" t="inlineStr"/>
-      <c r="FN3" t="b">
-        <v>0</v>
-      </c>
-      <c r="FO3" t="inlineStr"/>
+      <c r="FN3" t="inlineStr"/>
+      <c r="FO3" t="b">
+        <v>0</v>
+      </c>
       <c r="FP3" t="inlineStr"/>
-      <c r="FQ3" t="b">
-        <v>0</v>
-      </c>
-      <c r="FR3" t="inlineStr"/>
+      <c r="FQ3" t="inlineStr"/>
+      <c r="FR3" t="b">
+        <v>0</v>
+      </c>
       <c r="FS3" t="inlineStr"/>
-      <c r="FT3" t="b">
-        <v>0</v>
-      </c>
-      <c r="FU3" t="inlineStr"/>
+      <c r="FT3" t="inlineStr"/>
+      <c r="FU3" t="b">
+        <v>0</v>
+      </c>
       <c r="FV3" t="inlineStr"/>
-      <c r="FW3" t="b">
-        <v>0</v>
-      </c>
-      <c r="FX3" t="inlineStr"/>
+      <c r="FW3" t="inlineStr"/>
+      <c r="FX3" t="b">
+        <v>0</v>
+      </c>
       <c r="FY3" t="inlineStr"/>
-      <c r="FZ3" t="b">
-        <v>0</v>
-      </c>
-      <c r="GA3" t="inlineStr"/>
+      <c r="FZ3" t="inlineStr"/>
+      <c r="GA3" t="b">
+        <v>0</v>
+      </c>
       <c r="GB3" t="inlineStr"/>
-      <c r="GC3" t="b">
-        <v>0</v>
-      </c>
-      <c r="GD3" t="inlineStr"/>
+      <c r="GC3" t="inlineStr"/>
+      <c r="GD3" t="b">
+        <v>0</v>
+      </c>
       <c r="GE3" t="inlineStr"/>
-      <c r="GF3" t="b">
-        <v>0</v>
-      </c>
-      <c r="GG3" t="inlineStr"/>
+      <c r="GF3" t="inlineStr"/>
+      <c r="GG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="GH3" t="inlineStr"/>
+      <c r="GI3" t="inlineStr"/>
+      <c r="GJ3" t="b">
+        <v>0</v>
+      </c>
+      <c r="GK3" t="inlineStr"/>
+      <c r="GL3" t="inlineStr"/>
+      <c r="GM3" t="b">
+        <v>0</v>
+      </c>
+      <c r="GN3" t="inlineStr"/>
+      <c r="GO3" t="inlineStr"/>
+      <c r="GP3" t="b">
+        <v>0</v>
+      </c>
+      <c r="GQ3" t="inlineStr"/>
+      <c r="GR3" t="inlineStr"/>
+      <c r="GS3" t="b">
+        <v>0</v>
+      </c>
+      <c r="GT3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2087,344 +2241,681 @@
           <t>Santosh Pawar</t>
         </is>
       </c>
-      <c r="B4" t="n">
-        <v>87238949823784</v>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>9784563748</t>
+        </is>
       </c>
       <c r="C4" s="1" t="n">
-        <v>46169</v>
+        <v>46172</v>
       </c>
       <c r="D4" t="n">
-        <v>100000</v>
+        <v>5500000</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>JmD 1.0</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>2</v>
-      </c>
+          <t>JMD 6.0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="n">
-        <v>50000</v>
-      </c>
-      <c r="H4" s="1" t="n">
-        <v>46169</v>
-      </c>
-      <c r="I4" t="b">
-        <v>0</v>
-      </c>
-      <c r="J4" s="1" t="n">
-        <v>46508</v>
-      </c>
-      <c r="K4" t="b">
-        <v>1</v>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>27-05-2026 18:45:46</t>
-        </is>
-      </c>
-      <c r="M4" s="1" t="n">
-        <v>46169</v>
-      </c>
-      <c r="N4" t="b">
-        <v>1</v>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>27-05-2026 18:44:27</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="b">
-        <v>0</v>
-      </c>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="b">
-        <v>0</v>
-      </c>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="b">
-        <v>0</v>
-      </c>
-      <c r="X4" t="inlineStr"/>
+        <v>11000000</v>
+      </c>
+      <c r="H4" t="n">
+        <v>200</v>
+      </c>
+      <c r="I4" s="1" t="n">
+        <v>46876</v>
+      </c>
+      <c r="J4" t="b">
+        <v>0</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Ajay Bhosle</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>550000</v>
+      </c>
+      <c r="M4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+      <c r="O4" t="n">
+        <v>4</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>SBI Bank</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>Santosh Pawar</t>
+        </is>
+      </c>
+      <c r="R4" t="n">
+        <v>8283645789214</v>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>SBIN000938</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Thane</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>sdf675sdfsdf</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>MSDBF4535BNN</t>
+        </is>
+      </c>
+      <c r="W4" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="X4" t="b">
+        <v>0</v>
+      </c>
       <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA4" t="inlineStr"/>
+      <c r="Z4" s="1" t="n">
+        <v>46356</v>
+      </c>
+      <c r="AA4" t="b">
+        <v>0</v>
+      </c>
       <c r="AB4" t="inlineStr"/>
-      <c r="AC4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD4" t="inlineStr"/>
+      <c r="AC4" s="1" t="n">
+        <v>46446</v>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
       <c r="AE4" t="inlineStr"/>
-      <c r="AF4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="inlineStr"/>
+      <c r="AF4" s="1" t="n">
+        <v>46537</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
       <c r="AH4" t="inlineStr"/>
-      <c r="AI4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ4" t="inlineStr"/>
+      <c r="AI4" t="inlineStr"/>
+      <c r="AJ4" t="b">
+        <v>0</v>
+      </c>
       <c r="AK4" t="inlineStr"/>
-      <c r="AL4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AM4" t="inlineStr"/>
+      <c r="AL4" t="inlineStr"/>
+      <c r="AM4" t="b">
+        <v>0</v>
+      </c>
       <c r="AN4" t="inlineStr"/>
-      <c r="AO4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AP4" t="inlineStr"/>
+      <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="b">
+        <v>0</v>
+      </c>
       <c r="AQ4" t="inlineStr"/>
-      <c r="AR4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AS4" t="inlineStr"/>
+      <c r="AR4" t="inlineStr"/>
+      <c r="AS4" t="b">
+        <v>0</v>
+      </c>
       <c r="AT4" t="inlineStr"/>
-      <c r="AU4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AV4" t="inlineStr"/>
+      <c r="AU4" t="inlineStr"/>
+      <c r="AV4" t="b">
+        <v>0</v>
+      </c>
       <c r="AW4" t="inlineStr"/>
-      <c r="AX4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+      <c r="AX4" t="inlineStr"/>
+      <c r="AY4" t="b">
+        <v>0</v>
+      </c>
       <c r="AZ4" t="inlineStr"/>
-      <c r="BA4" t="b">
-        <v>0</v>
-      </c>
-      <c r="BB4" t="inlineStr"/>
+      <c r="BA4" t="inlineStr"/>
+      <c r="BB4" t="b">
+        <v>0</v>
+      </c>
       <c r="BC4" t="inlineStr"/>
-      <c r="BD4" t="b">
-        <v>0</v>
-      </c>
-      <c r="BE4" t="inlineStr"/>
+      <c r="BD4" t="inlineStr"/>
+      <c r="BE4" t="b">
+        <v>0</v>
+      </c>
       <c r="BF4" t="inlineStr"/>
-      <c r="BG4" t="b">
-        <v>0</v>
-      </c>
-      <c r="BH4" t="inlineStr"/>
+      <c r="BG4" t="inlineStr"/>
+      <c r="BH4" t="b">
+        <v>0</v>
+      </c>
       <c r="BI4" t="inlineStr"/>
-      <c r="BJ4" t="b">
-        <v>0</v>
-      </c>
-      <c r="BK4" t="inlineStr"/>
+      <c r="BJ4" t="inlineStr"/>
+      <c r="BK4" t="b">
+        <v>0</v>
+      </c>
       <c r="BL4" t="inlineStr"/>
-      <c r="BM4" t="b">
-        <v>0</v>
-      </c>
-      <c r="BN4" t="inlineStr"/>
+      <c r="BM4" t="inlineStr"/>
+      <c r="BN4" t="b">
+        <v>0</v>
+      </c>
       <c r="BO4" t="inlineStr"/>
-      <c r="BP4" t="b">
-        <v>0</v>
-      </c>
-      <c r="BQ4" t="inlineStr"/>
+      <c r="BP4" t="inlineStr"/>
+      <c r="BQ4" t="b">
+        <v>0</v>
+      </c>
       <c r="BR4" t="inlineStr"/>
-      <c r="BS4" t="b">
-        <v>0</v>
-      </c>
-      <c r="BT4" t="inlineStr"/>
+      <c r="BS4" t="inlineStr"/>
+      <c r="BT4" t="b">
+        <v>0</v>
+      </c>
       <c r="BU4" t="inlineStr"/>
-      <c r="BV4" t="b">
-        <v>0</v>
-      </c>
-      <c r="BW4" t="inlineStr"/>
+      <c r="BV4" t="inlineStr"/>
+      <c r="BW4" t="b">
+        <v>0</v>
+      </c>
       <c r="BX4" t="inlineStr"/>
-      <c r="BY4" t="b">
-        <v>0</v>
-      </c>
-      <c r="BZ4" t="inlineStr"/>
+      <c r="BY4" t="inlineStr"/>
+      <c r="BZ4" t="b">
+        <v>0</v>
+      </c>
       <c r="CA4" t="inlineStr"/>
-      <c r="CB4" t="b">
-        <v>0</v>
-      </c>
-      <c r="CC4" t="inlineStr"/>
+      <c r="CB4" t="inlineStr"/>
+      <c r="CC4" t="b">
+        <v>0</v>
+      </c>
       <c r="CD4" t="inlineStr"/>
-      <c r="CE4" t="b">
-        <v>0</v>
-      </c>
-      <c r="CF4" t="inlineStr"/>
+      <c r="CE4" t="inlineStr"/>
+      <c r="CF4" t="b">
+        <v>0</v>
+      </c>
       <c r="CG4" t="inlineStr"/>
-      <c r="CH4" t="b">
-        <v>0</v>
-      </c>
-      <c r="CI4" t="inlineStr"/>
+      <c r="CH4" t="inlineStr"/>
+      <c r="CI4" t="b">
+        <v>0</v>
+      </c>
       <c r="CJ4" t="inlineStr"/>
-      <c r="CK4" t="b">
-        <v>0</v>
-      </c>
-      <c r="CL4" t="inlineStr"/>
+      <c r="CK4" t="inlineStr"/>
+      <c r="CL4" t="b">
+        <v>0</v>
+      </c>
       <c r="CM4" t="inlineStr"/>
-      <c r="CN4" t="b">
-        <v>0</v>
-      </c>
-      <c r="CO4" t="inlineStr"/>
+      <c r="CN4" t="inlineStr"/>
+      <c r="CO4" t="b">
+        <v>0</v>
+      </c>
       <c r="CP4" t="inlineStr"/>
-      <c r="CQ4" t="b">
-        <v>0</v>
-      </c>
-      <c r="CR4" t="inlineStr"/>
+      <c r="CQ4" t="inlineStr"/>
+      <c r="CR4" t="b">
+        <v>0</v>
+      </c>
       <c r="CS4" t="inlineStr"/>
-      <c r="CT4" t="b">
-        <v>0</v>
-      </c>
-      <c r="CU4" t="inlineStr"/>
+      <c r="CT4" t="inlineStr"/>
+      <c r="CU4" t="b">
+        <v>0</v>
+      </c>
       <c r="CV4" t="inlineStr"/>
-      <c r="CW4" t="b">
-        <v>0</v>
-      </c>
-      <c r="CX4" t="inlineStr"/>
+      <c r="CW4" t="inlineStr"/>
+      <c r="CX4" t="b">
+        <v>0</v>
+      </c>
       <c r="CY4" t="inlineStr"/>
-      <c r="CZ4" t="b">
-        <v>0</v>
-      </c>
-      <c r="DA4" t="inlineStr"/>
+      <c r="CZ4" t="inlineStr"/>
+      <c r="DA4" t="b">
+        <v>0</v>
+      </c>
       <c r="DB4" t="inlineStr"/>
-      <c r="DC4" t="b">
-        <v>0</v>
-      </c>
-      <c r="DD4" t="inlineStr"/>
+      <c r="DC4" t="inlineStr"/>
+      <c r="DD4" t="b">
+        <v>0</v>
+      </c>
       <c r="DE4" t="inlineStr"/>
-      <c r="DF4" t="b">
-        <v>0</v>
-      </c>
-      <c r="DG4" t="inlineStr"/>
+      <c r="DF4" t="inlineStr"/>
+      <c r="DG4" t="b">
+        <v>0</v>
+      </c>
       <c r="DH4" t="inlineStr"/>
-      <c r="DI4" t="b">
-        <v>0</v>
-      </c>
-      <c r="DJ4" t="inlineStr"/>
+      <c r="DI4" t="inlineStr"/>
+      <c r="DJ4" t="b">
+        <v>0</v>
+      </c>
       <c r="DK4" t="inlineStr"/>
-      <c r="DL4" t="b">
-        <v>0</v>
-      </c>
-      <c r="DM4" t="inlineStr"/>
+      <c r="DL4" t="inlineStr"/>
+      <c r="DM4" t="b">
+        <v>0</v>
+      </c>
       <c r="DN4" t="inlineStr"/>
-      <c r="DO4" t="b">
-        <v>0</v>
-      </c>
-      <c r="DP4" t="inlineStr"/>
+      <c r="DO4" t="inlineStr"/>
+      <c r="DP4" t="b">
+        <v>0</v>
+      </c>
       <c r="DQ4" t="inlineStr"/>
-      <c r="DR4" t="b">
-        <v>0</v>
-      </c>
-      <c r="DS4" t="inlineStr"/>
+      <c r="DR4" t="inlineStr"/>
+      <c r="DS4" t="b">
+        <v>0</v>
+      </c>
       <c r="DT4" t="inlineStr"/>
-      <c r="DU4" t="b">
-        <v>0</v>
-      </c>
-      <c r="DV4" t="inlineStr"/>
+      <c r="DU4" t="inlineStr"/>
+      <c r="DV4" t="b">
+        <v>0</v>
+      </c>
       <c r="DW4" t="inlineStr"/>
-      <c r="DX4" t="b">
-        <v>0</v>
-      </c>
-      <c r="DY4" t="inlineStr"/>
+      <c r="DX4" t="inlineStr"/>
+      <c r="DY4" t="b">
+        <v>0</v>
+      </c>
       <c r="DZ4" t="inlineStr"/>
-      <c r="EA4" t="b">
-        <v>0</v>
-      </c>
-      <c r="EB4" t="inlineStr"/>
+      <c r="EA4" t="inlineStr"/>
+      <c r="EB4" t="b">
+        <v>0</v>
+      </c>
       <c r="EC4" t="inlineStr"/>
-      <c r="ED4" t="b">
-        <v>0</v>
-      </c>
-      <c r="EE4" t="inlineStr"/>
+      <c r="ED4" t="inlineStr"/>
+      <c r="EE4" t="b">
+        <v>0</v>
+      </c>
       <c r="EF4" t="inlineStr"/>
-      <c r="EG4" t="b">
-        <v>0</v>
-      </c>
-      <c r="EH4" t="inlineStr"/>
+      <c r="EG4" t="inlineStr"/>
+      <c r="EH4" t="b">
+        <v>0</v>
+      </c>
       <c r="EI4" t="inlineStr"/>
-      <c r="EJ4" t="b">
-        <v>0</v>
-      </c>
-      <c r="EK4" t="inlineStr"/>
+      <c r="EJ4" t="inlineStr"/>
+      <c r="EK4" t="b">
+        <v>0</v>
+      </c>
       <c r="EL4" t="inlineStr"/>
-      <c r="EM4" t="b">
-        <v>0</v>
-      </c>
-      <c r="EN4" t="inlineStr"/>
+      <c r="EM4" t="inlineStr"/>
+      <c r="EN4" t="b">
+        <v>0</v>
+      </c>
       <c r="EO4" t="inlineStr"/>
-      <c r="EP4" t="b">
-        <v>0</v>
-      </c>
-      <c r="EQ4" t="inlineStr"/>
+      <c r="EP4" t="inlineStr"/>
+      <c r="EQ4" t="b">
+        <v>0</v>
+      </c>
       <c r="ER4" t="inlineStr"/>
-      <c r="ES4" t="b">
-        <v>0</v>
-      </c>
-      <c r="ET4" t="inlineStr"/>
+      <c r="ES4" t="inlineStr"/>
+      <c r="ET4" t="b">
+        <v>0</v>
+      </c>
       <c r="EU4" t="inlineStr"/>
-      <c r="EV4" t="b">
-        <v>0</v>
-      </c>
-      <c r="EW4" t="inlineStr"/>
+      <c r="EV4" t="inlineStr"/>
+      <c r="EW4" t="b">
+        <v>0</v>
+      </c>
       <c r="EX4" t="inlineStr"/>
-      <c r="EY4" t="b">
-        <v>0</v>
-      </c>
-      <c r="EZ4" t="inlineStr"/>
+      <c r="EY4" t="inlineStr"/>
+      <c r="EZ4" t="b">
+        <v>0</v>
+      </c>
       <c r="FA4" t="inlineStr"/>
-      <c r="FB4" t="b">
-        <v>0</v>
-      </c>
-      <c r="FC4" t="inlineStr"/>
+      <c r="FB4" t="inlineStr"/>
+      <c r="FC4" t="b">
+        <v>0</v>
+      </c>
       <c r="FD4" t="inlineStr"/>
-      <c r="FE4" t="b">
-        <v>0</v>
-      </c>
-      <c r="FF4" t="inlineStr"/>
+      <c r="FE4" t="inlineStr"/>
+      <c r="FF4" t="b">
+        <v>0</v>
+      </c>
       <c r="FG4" t="inlineStr"/>
-      <c r="FH4" t="b">
-        <v>0</v>
-      </c>
-      <c r="FI4" t="inlineStr"/>
+      <c r="FH4" t="inlineStr"/>
+      <c r="FI4" t="b">
+        <v>0</v>
+      </c>
       <c r="FJ4" t="inlineStr"/>
-      <c r="FK4" t="b">
-        <v>0</v>
-      </c>
-      <c r="FL4" t="inlineStr"/>
+      <c r="FK4" t="inlineStr"/>
+      <c r="FL4" t="b">
+        <v>0</v>
+      </c>
       <c r="FM4" t="inlineStr"/>
-      <c r="FN4" t="b">
-        <v>0</v>
-      </c>
-      <c r="FO4" t="inlineStr"/>
+      <c r="FN4" t="inlineStr"/>
+      <c r="FO4" t="b">
+        <v>0</v>
+      </c>
       <c r="FP4" t="inlineStr"/>
-      <c r="FQ4" t="b">
-        <v>0</v>
-      </c>
-      <c r="FR4" t="inlineStr"/>
+      <c r="FQ4" t="inlineStr"/>
+      <c r="FR4" t="b">
+        <v>0</v>
+      </c>
       <c r="FS4" t="inlineStr"/>
-      <c r="FT4" t="b">
-        <v>0</v>
-      </c>
-      <c r="FU4" t="inlineStr"/>
+      <c r="FT4" t="inlineStr"/>
+      <c r="FU4" t="b">
+        <v>0</v>
+      </c>
       <c r="FV4" t="inlineStr"/>
-      <c r="FW4" t="b">
-        <v>0</v>
-      </c>
-      <c r="FX4" t="inlineStr"/>
+      <c r="FW4" t="inlineStr"/>
+      <c r="FX4" t="b">
+        <v>0</v>
+      </c>
       <c r="FY4" t="inlineStr"/>
-      <c r="FZ4" t="b">
-        <v>0</v>
-      </c>
-      <c r="GA4" t="inlineStr"/>
+      <c r="FZ4" t="inlineStr"/>
+      <c r="GA4" t="b">
+        <v>0</v>
+      </c>
       <c r="GB4" t="inlineStr"/>
-      <c r="GC4" t="b">
-        <v>0</v>
-      </c>
-      <c r="GD4" t="inlineStr"/>
+      <c r="GC4" t="inlineStr"/>
+      <c r="GD4" t="b">
+        <v>0</v>
+      </c>
       <c r="GE4" t="inlineStr"/>
-      <c r="GF4" t="b">
-        <v>0</v>
-      </c>
-      <c r="GG4" t="inlineStr"/>
+      <c r="GF4" t="inlineStr"/>
+      <c r="GG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="GH4" t="inlineStr"/>
+      <c r="GI4" t="inlineStr"/>
+      <c r="GJ4" t="b">
+        <v>0</v>
+      </c>
+      <c r="GK4" t="inlineStr"/>
+      <c r="GL4" t="inlineStr"/>
+      <c r="GM4" t="b">
+        <v>0</v>
+      </c>
+      <c r="GN4" t="inlineStr"/>
+      <c r="GO4" t="inlineStr"/>
+      <c r="GP4" t="b">
+        <v>0</v>
+      </c>
+      <c r="GQ4" t="inlineStr"/>
+      <c r="GR4" t="inlineStr"/>
+      <c r="GS4" t="b">
+        <v>0</v>
+      </c>
+      <c r="GT4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Vishal Chawan</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>98534834567</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>JMD 5.0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="H5" t="n">
+        <v>100</v>
+      </c>
+      <c r="I5" s="2" t="n">
+        <v>46172</v>
+      </c>
+      <c r="J5" t="b">
+        <v>0</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Nikhil Bhosle</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>400000</v>
+      </c>
+      <c r="M5" t="b">
+        <v>0</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Half-Yearly</t>
+        </is>
+      </c>
+      <c r="O5" t="n">
+        <v>4</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>ICICI Bank</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>Vishal Chavan</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>87642387478623</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>ICIC0000542</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Vashi</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>VNVNVBNVBN788V</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>DSNVFLJD467SDF</t>
+        </is>
+      </c>
+      <c r="W5" s="2" t="n">
+        <v>46172</v>
+      </c>
+      <c r="X5" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" s="2" t="n">
+        <v>46537</v>
+      </c>
+      <c r="AA5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" s="2" t="n">
+        <v>46721</v>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="inlineStr"/>
+      <c r="AF5" s="2" t="n">
+        <v>46903</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr"/>
+      <c r="AJ5" t="inlineStr"/>
+      <c r="AK5" t="inlineStr"/>
+      <c r="AL5" t="inlineStr"/>
+      <c r="AM5" t="inlineStr"/>
+      <c r="AN5" t="inlineStr"/>
+      <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="inlineStr"/>
+      <c r="AQ5" t="inlineStr"/>
+      <c r="AR5" t="inlineStr"/>
+      <c r="AS5" t="inlineStr"/>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AU5" t="inlineStr"/>
+      <c r="AV5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr"/>
+      <c r="AX5" t="inlineStr"/>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr"/>
+      <c r="BA5" t="inlineStr"/>
+      <c r="BB5" t="inlineStr"/>
+      <c r="BC5" t="inlineStr"/>
+      <c r="BD5" t="inlineStr"/>
+      <c r="BE5" t="inlineStr"/>
+      <c r="BF5" t="inlineStr"/>
+      <c r="BG5" t="inlineStr"/>
+      <c r="BH5" t="inlineStr"/>
+      <c r="BI5" t="inlineStr"/>
+      <c r="BJ5" t="inlineStr"/>
+      <c r="BK5" t="inlineStr"/>
+      <c r="BL5" t="inlineStr"/>
+      <c r="BM5" t="inlineStr"/>
+      <c r="BN5" t="inlineStr"/>
+      <c r="BO5" t="inlineStr"/>
+      <c r="BP5" t="inlineStr"/>
+      <c r="BQ5" t="inlineStr"/>
+      <c r="BR5" t="inlineStr"/>
+      <c r="BS5" t="inlineStr"/>
+      <c r="BT5" t="inlineStr"/>
+      <c r="BU5" t="inlineStr"/>
+      <c r="BV5" t="inlineStr"/>
+      <c r="BW5" t="inlineStr"/>
+      <c r="BX5" t="inlineStr"/>
+      <c r="BY5" t="inlineStr"/>
+      <c r="BZ5" t="inlineStr"/>
+      <c r="CA5" t="inlineStr"/>
+      <c r="CB5" t="inlineStr"/>
+      <c r="CC5" t="inlineStr"/>
+      <c r="CD5" t="inlineStr"/>
+      <c r="CE5" t="inlineStr"/>
+      <c r="CF5" t="inlineStr"/>
+      <c r="CG5" t="inlineStr"/>
+      <c r="CH5" t="inlineStr"/>
+      <c r="CI5" t="inlineStr"/>
+      <c r="CJ5" t="inlineStr"/>
+      <c r="CK5" t="inlineStr"/>
+      <c r="CL5" t="inlineStr"/>
+      <c r="CM5" t="inlineStr"/>
+      <c r="CN5" t="inlineStr"/>
+      <c r="CO5" t="inlineStr"/>
+      <c r="CP5" t="inlineStr"/>
+      <c r="CQ5" t="inlineStr"/>
+      <c r="CR5" t="inlineStr"/>
+      <c r="CS5" t="inlineStr"/>
+      <c r="CT5" t="inlineStr"/>
+      <c r="CU5" t="inlineStr"/>
+      <c r="CV5" t="inlineStr"/>
+      <c r="CW5" t="inlineStr"/>
+      <c r="CX5" t="inlineStr"/>
+      <c r="CY5" t="inlineStr"/>
+      <c r="CZ5" t="inlineStr"/>
+      <c r="DA5" t="inlineStr"/>
+      <c r="DB5" t="inlineStr"/>
+      <c r="DC5" t="inlineStr"/>
+      <c r="DD5" t="inlineStr"/>
+      <c r="DE5" t="inlineStr"/>
+      <c r="DF5" t="inlineStr"/>
+      <c r="DG5" t="inlineStr"/>
+      <c r="DH5" t="inlineStr"/>
+      <c r="DI5" t="inlineStr"/>
+      <c r="DJ5" t="inlineStr"/>
+      <c r="DK5" t="inlineStr"/>
+      <c r="DL5" t="inlineStr"/>
+      <c r="DM5" t="inlineStr"/>
+      <c r="DN5" t="inlineStr"/>
+      <c r="DO5" t="inlineStr"/>
+      <c r="DP5" t="inlineStr"/>
+      <c r="DQ5" t="inlineStr"/>
+      <c r="DR5" t="inlineStr"/>
+      <c r="DS5" t="inlineStr"/>
+      <c r="DT5" t="inlineStr"/>
+      <c r="DU5" t="inlineStr"/>
+      <c r="DV5" t="inlineStr"/>
+      <c r="DW5" t="inlineStr"/>
+      <c r="DX5" t="inlineStr"/>
+      <c r="DY5" t="inlineStr"/>
+      <c r="DZ5" t="inlineStr"/>
+      <c r="EA5" t="inlineStr"/>
+      <c r="EB5" t="inlineStr"/>
+      <c r="EC5" t="inlineStr"/>
+      <c r="ED5" t="inlineStr"/>
+      <c r="EE5" t="inlineStr"/>
+      <c r="EF5" t="inlineStr"/>
+      <c r="EG5" t="inlineStr"/>
+      <c r="EH5" t="inlineStr"/>
+      <c r="EI5" t="inlineStr"/>
+      <c r="EJ5" t="inlineStr"/>
+      <c r="EK5" t="inlineStr"/>
+      <c r="EL5" t="inlineStr"/>
+      <c r="EM5" t="inlineStr"/>
+      <c r="EN5" t="inlineStr"/>
+      <c r="EO5" t="inlineStr"/>
+      <c r="EP5" t="inlineStr"/>
+      <c r="EQ5" t="inlineStr"/>
+      <c r="ER5" t="inlineStr"/>
+      <c r="ES5" t="inlineStr"/>
+      <c r="ET5" t="inlineStr"/>
+      <c r="EU5" t="inlineStr"/>
+      <c r="EV5" t="inlineStr"/>
+      <c r="EW5" t="inlineStr"/>
+      <c r="EX5" t="inlineStr"/>
+      <c r="EY5" t="inlineStr"/>
+      <c r="EZ5" t="inlineStr"/>
+      <c r="FA5" t="inlineStr"/>
+      <c r="FB5" t="inlineStr"/>
+      <c r="FC5" t="inlineStr"/>
+      <c r="FD5" t="inlineStr"/>
+      <c r="FE5" t="inlineStr"/>
+      <c r="FF5" t="inlineStr"/>
+      <c r="FG5" t="inlineStr"/>
+      <c r="FH5" t="inlineStr"/>
+      <c r="FI5" t="inlineStr"/>
+      <c r="FJ5" t="inlineStr"/>
+      <c r="FK5" t="inlineStr"/>
+      <c r="FL5" t="inlineStr"/>
+      <c r="FM5" t="inlineStr"/>
+      <c r="FN5" t="inlineStr"/>
+      <c r="FO5" t="inlineStr"/>
+      <c r="FP5" t="inlineStr"/>
+      <c r="FQ5" t="inlineStr"/>
+      <c r="FR5" t="inlineStr"/>
+      <c r="FS5" t="inlineStr"/>
+      <c r="FT5" t="inlineStr"/>
+      <c r="FU5" t="inlineStr"/>
+      <c r="FV5" t="inlineStr"/>
+      <c r="FW5" t="inlineStr"/>
+      <c r="FX5" t="inlineStr"/>
+      <c r="FY5" t="inlineStr"/>
+      <c r="FZ5" t="inlineStr"/>
+      <c r="GA5" t="inlineStr"/>
+      <c r="GB5" t="inlineStr"/>
+      <c r="GC5" t="inlineStr"/>
+      <c r="GD5" t="inlineStr"/>
+      <c r="GE5" t="inlineStr"/>
+      <c r="GF5" t="inlineStr"/>
+      <c r="GG5" t="inlineStr"/>
+      <c r="GH5" t="inlineStr"/>
+      <c r="GI5" t="inlineStr"/>
+      <c r="GJ5" t="inlineStr"/>
+      <c r="GK5" t="inlineStr"/>
+      <c r="GL5" t="inlineStr"/>
+      <c r="GM5" t="inlineStr"/>
+      <c r="GN5" t="inlineStr"/>
+      <c r="GO5" t="inlineStr"/>
+      <c r="GP5" t="inlineStr"/>
+      <c r="GQ5" t="inlineStr"/>
+      <c r="GR5" t="inlineStr"/>
+      <c r="GS5" t="inlineStr"/>
+      <c r="GT5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
